--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779296</v>
+        <v>122779298</v>
       </c>
       <c r="B19" t="n">
-        <v>56680</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2888,7 +2888,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2898,13 +2898,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507257</v>
+        <v>507119</v>
       </c>
       <c r="R19" t="n">
-        <v>7053479</v>
+        <v>7053255</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2955,9 +2955,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2978,7 +2993,7 @@
         <v>122779282</v>
       </c>
       <c r="B20" t="n">
-        <v>79879</v>
+        <v>79883</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3120,10 +3135,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779272</v>
+        <v>122779331</v>
       </c>
       <c r="B21" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3136,30 +3151,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3167,13 +3178,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507186</v>
+        <v>507003</v>
       </c>
       <c r="R21" t="n">
-        <v>7053514</v>
+        <v>7053201</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3203,6 +3214,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3217,12 +3233,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3237,12 +3248,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3263,7 +3274,7 @@
         <v>122779277</v>
       </c>
       <c r="B22" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3403,7 +3414,7 @@
         <v>122779265</v>
       </c>
       <c r="B23" t="n">
-        <v>90936</v>
+        <v>90940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3535,10 +3546,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779331</v>
+        <v>122779296</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>56680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3551,40 +3562,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507003</v>
+        <v>507257</v>
       </c>
       <c r="R24" t="n">
-        <v>7053201</v>
+        <v>7053479</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3618,7 +3634,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3627,33 +3643,17 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779298</v>
+        <v>122779318</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3687,45 +3687,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507119</v>
+        <v>507101</v>
       </c>
       <c r="R25" t="n">
-        <v>7053255</v>
+        <v>7053264</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3759,7 +3758,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3768,6 +3767,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3776,24 +3776,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779318</v>
+        <v>122779272</v>
       </c>
       <c r="B26" t="n">
-        <v>79843</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3827,28 +3832,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3858,10 +3863,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507101</v>
+        <v>507186</v>
       </c>
       <c r="R26" t="n">
-        <v>7053264</v>
+        <v>7053514</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3896,11 +3901,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3918,27 +3918,27 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779298</v>
+        <v>122779277</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,45 +2866,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507119</v>
+        <v>507098</v>
       </c>
       <c r="R19" t="n">
-        <v>7053255</v>
+        <v>7053554</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2947,6 +2946,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2957,22 +2957,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779282</v>
+        <v>122779265</v>
       </c>
       <c r="B20" t="n">
-        <v>79883</v>
+        <v>90940</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3002,32 +3002,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507098</v>
+        <v>507188</v>
       </c>
       <c r="R20" t="n">
-        <v>7053554</v>
+        <v>7053524</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3073,11 +3073,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3097,27 +3092,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3135,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779331</v>
+        <v>122779298</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3151,37 +3141,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507003</v>
+        <v>507119</v>
       </c>
       <c r="R21" t="n">
-        <v>7053201</v>
+        <v>7053255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3218,7 +3213,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3227,13 +3222,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3248,12 +3242,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3271,10 +3265,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779277</v>
+        <v>122779282</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3283,25 +3277,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3358,7 +3352,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3374,6 +3368,11 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3411,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779265</v>
+        <v>122779331</v>
       </c>
       <c r="B23" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3427,30 +3426,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507188</v>
+        <v>507003</v>
       </c>
       <c r="R23" t="n">
-        <v>7053524</v>
+        <v>7053201</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3496,6 +3491,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3508,12 +3508,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3526,9 +3521,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779296</v>
+        <v>122779272</v>
       </c>
       <c r="B24" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3562,42 +3562,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507257</v>
+        <v>507186</v>
       </c>
       <c r="R24" t="n">
-        <v>7053479</v>
+        <v>7053514</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3632,17 +3631,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3654,6 +3649,26 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>Gammal grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3671,10 +3686,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779318</v>
+        <v>122779296</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3687,41 +3702,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507101</v>
+        <v>507257</v>
       </c>
       <c r="R25" t="n">
-        <v>7053264</v>
+        <v>7053479</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3758,7 +3774,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3767,7 +3783,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3778,27 +3793,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779272</v>
+        <v>122779318</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3832,28 +3827,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507186</v>
+        <v>507101</v>
       </c>
       <c r="R26" t="n">
-        <v>7053514</v>
+        <v>7053264</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3901,6 +3896,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3918,27 +3918,27 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3265,10 +3265,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779282</v>
+        <v>122779318</v>
       </c>
       <c r="B22" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3277,25 +3277,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507098</v>
+        <v>507101</v>
       </c>
       <c r="R22" t="n">
-        <v>7053554</v>
+        <v>7053264</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3372,17 +3372,17 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779331</v>
+        <v>122779296</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3426,40 +3426,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507003</v>
+        <v>507257</v>
       </c>
       <c r="R23" t="n">
-        <v>7053201</v>
+        <v>7053479</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3493,7 +3498,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3502,33 +3507,17 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3546,10 +3535,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779272</v>
+        <v>122779282</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>79883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3558,32 +3547,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3593,10 +3582,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507186</v>
+        <v>507098</v>
       </c>
       <c r="R24" t="n">
-        <v>7053514</v>
+        <v>7053554</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3631,6 +3620,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3648,27 +3642,27 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3686,10 +3680,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779296</v>
+        <v>122779272</v>
       </c>
       <c r="B25" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3702,42 +3696,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507257</v>
+        <v>507186</v>
       </c>
       <c r="R25" t="n">
-        <v>7053479</v>
+        <v>7053514</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3772,17 +3765,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3794,6 +3783,26 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>Gammal grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3811,10 +3820,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3827,30 +3836,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3858,13 +3863,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R26" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3913,32 +3918,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779277</v>
+        <v>122779272</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,28 +2866,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507098</v>
+        <v>507186</v>
       </c>
       <c r="R19" t="n">
-        <v>7053554</v>
+        <v>7053514</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2935,11 +2935,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2955,24 +2950,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779265</v>
+        <v>122779331</v>
       </c>
       <c r="B20" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,30 +3006,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3037,10 +3033,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507188</v>
+        <v>507003</v>
       </c>
       <c r="R20" t="n">
-        <v>7053524</v>
+        <v>7053201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3075,6 +3071,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3087,12 +3088,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3105,9 +3101,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3125,10 +3126,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779298</v>
+        <v>122779296</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3141,16 +3142,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3163,7 +3164,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3173,13 +3174,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507119</v>
+        <v>507257</v>
       </c>
       <c r="R21" t="n">
-        <v>7053255</v>
+        <v>7053479</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3213,7 +3214,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3230,24 +3231,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3265,10 +3251,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779318</v>
+        <v>122779265</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>90940</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3281,28 +3267,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3312,13 +3298,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507101</v>
+        <v>507188</v>
       </c>
       <c r="R22" t="n">
-        <v>7053264</v>
+        <v>7053524</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3348,11 +3334,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3377,22 +3358,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3386,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779296</v>
+        <v>122779277</v>
       </c>
       <c r="B23" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3426,42 +3402,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507257</v>
+        <v>507098</v>
       </c>
       <c r="R23" t="n">
-        <v>7053479</v>
+        <v>7053554</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3498,7 +3473,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3507,6 +3482,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3515,9 +3491,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3680,10 +3671,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779272</v>
+        <v>122779298</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3696,44 +3687,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507186</v>
+        <v>507119</v>
       </c>
       <c r="R25" t="n">
-        <v>7053514</v>
+        <v>7053255</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3765,13 +3757,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3780,11 +3776,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3797,12 +3788,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3820,10 +3811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779331</v>
+        <v>122779318</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3836,26 +3827,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3863,13 +3858,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507003</v>
+        <v>507101</v>
       </c>
       <c r="R26" t="n">
-        <v>7053201</v>
+        <v>7053264</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3918,27 +3913,32 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779272</v>
+        <v>122779277</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,28 +2866,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507186</v>
+        <v>507098</v>
       </c>
       <c r="R19" t="n">
-        <v>7053514</v>
+        <v>7053554</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2935,6 +2935,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2950,29 +2955,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779331</v>
+        <v>122779318</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,26 +3006,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3033,13 +3037,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507003</v>
+        <v>507101</v>
       </c>
       <c r="R20" t="n">
-        <v>7053201</v>
+        <v>7053264</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3073,7 +3077,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3088,27 +3092,32 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3126,10 +3135,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779296</v>
+        <v>122779272</v>
       </c>
       <c r="B21" t="n">
-        <v>56680</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,42 +3151,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507257</v>
+        <v>507186</v>
       </c>
       <c r="R21" t="n">
-        <v>7053479</v>
+        <v>7053514</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3212,17 +3220,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3234,6 +3238,26 @@
       <c r="AI21" t="inlineStr">
         <is>
           <t>Gammal grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3251,10 +3275,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779265</v>
+        <v>122779296</v>
       </c>
       <c r="B22" t="n">
-        <v>90940</v>
+        <v>56680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3267,44 +3291,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507188</v>
+        <v>507257</v>
       </c>
       <c r="R22" t="n">
-        <v>7053524</v>
+        <v>7053479</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3336,13 +3361,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3353,22 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3386,10 +3400,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779277</v>
+        <v>122779282</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3398,25 +3412,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3473,7 +3487,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3489,6 +3503,11 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3526,10 +3545,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779282</v>
+        <v>122779331</v>
       </c>
       <c r="B24" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3538,34 +3557,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3573,13 +3588,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507098</v>
+        <v>507003</v>
       </c>
       <c r="R24" t="n">
-        <v>7053554</v>
+        <v>7053201</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3613,7 +3628,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3628,32 +3643,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3671,10 +3681,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779298</v>
+        <v>122779265</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>90948</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3687,42 +3697,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507119</v>
+        <v>507188</v>
       </c>
       <c r="R25" t="n">
-        <v>7053255</v>
+        <v>7053524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3757,17 +3766,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3776,6 +3781,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3786,14 +3796,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779318</v>
+        <v>122779298</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3827,44 +3832,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507101</v>
+        <v>507119</v>
       </c>
       <c r="R26" t="n">
-        <v>7053264</v>
+        <v>7053255</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3898,7 +3904,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3907,7 +3913,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3916,29 +3921,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779277</v>
+        <v>122779282</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2862,25 +2862,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2953,6 +2953,11 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2990,10 +2995,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779318</v>
+        <v>122779265</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,28 +3011,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3037,13 +3042,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507101</v>
+        <v>507188</v>
       </c>
       <c r="R20" t="n">
-        <v>7053264</v>
+        <v>7053524</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3073,11 +3078,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3102,22 +3102,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3135,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779272</v>
+        <v>122779277</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3151,28 +3146,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3182,10 +3177,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507186</v>
+        <v>507098</v>
       </c>
       <c r="R21" t="n">
-        <v>7053514</v>
+        <v>7053554</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3220,6 +3215,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3235,29 +3235,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3275,10 +3270,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779296</v>
+        <v>122779272</v>
       </c>
       <c r="B22" t="n">
-        <v>56680</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3291,42 +3286,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507257</v>
+        <v>507186</v>
       </c>
       <c r="R22" t="n">
-        <v>7053479</v>
+        <v>7053514</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3361,17 +3355,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3383,6 +3373,26 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>Gammal grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3400,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779282</v>
+        <v>122779318</v>
       </c>
       <c r="B23" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3412,25 +3422,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3447,10 +3457,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507098</v>
+        <v>507101</v>
       </c>
       <c r="R23" t="n">
-        <v>7053554</v>
+        <v>7053264</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3487,7 +3497,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3507,17 +3517,17 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3527,7 +3537,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,10 +3555,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779331</v>
+        <v>122779296</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3561,40 +3571,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507003</v>
+        <v>507257</v>
       </c>
       <c r="R24" t="n">
-        <v>7053201</v>
+        <v>7053479</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3628,7 +3643,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3637,33 +3652,17 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3681,10 +3680,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779265</v>
+        <v>122779331</v>
       </c>
       <c r="B25" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3697,30 +3696,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3728,10 +3723,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507188</v>
+        <v>507003</v>
       </c>
       <c r="R25" t="n">
-        <v>7053524</v>
+        <v>7053201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3766,6 +3761,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3778,12 +3778,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3796,9 +3791,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779282</v>
+        <v>122779296</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>56680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2862,45 +2862,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507098</v>
+        <v>507257</v>
       </c>
       <c r="R19" t="n">
-        <v>7053554</v>
+        <v>7053479</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2937,7 +2938,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2946,7 +2947,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2957,27 +2957,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2995,10 +2975,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779265</v>
+        <v>122779272</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3011,21 +2991,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3042,13 +3022,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507188</v>
+        <v>507186</v>
       </c>
       <c r="R20" t="n">
-        <v>7053524</v>
+        <v>7053514</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3097,7 +3077,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3110,9 +3090,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3270,10 +3255,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779272</v>
+        <v>122779298</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3286,44 +3271,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507186</v>
+        <v>507119</v>
       </c>
       <c r="R22" t="n">
-        <v>7053514</v>
+        <v>7053255</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3355,13 +3341,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3370,11 +3360,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3387,12 +3372,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3555,10 +3540,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779296</v>
+        <v>122779265</v>
       </c>
       <c r="B24" t="n">
-        <v>56680</v>
+        <v>90948</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3571,45 +3556,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507257</v>
+        <v>507188</v>
       </c>
       <c r="R24" t="n">
-        <v>7053479</v>
+        <v>7053524</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3641,17 +3625,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3662,7 +3642,22 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779298</v>
+        <v>122779282</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>79883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3828,49 +3823,48 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507119</v>
+        <v>507098</v>
       </c>
       <c r="R26" t="n">
-        <v>7053255</v>
+        <v>7053554</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3904,7 +3898,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3913,6 +3907,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3921,24 +3916,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779296</v>
+        <v>122779277</v>
       </c>
       <c r="B19" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,42 +2866,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507257</v>
+        <v>507098</v>
       </c>
       <c r="R19" t="n">
-        <v>7053479</v>
+        <v>7053554</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2947,6 +2946,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2955,9 +2955,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2975,10 +2990,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779272</v>
+        <v>122779298</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2991,44 +3006,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507186</v>
+        <v>507119</v>
       </c>
       <c r="R20" t="n">
-        <v>7053514</v>
+        <v>7053255</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3060,13 +3076,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3075,11 +3095,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3092,12 +3107,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3115,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779277</v>
+        <v>122779282</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3127,25 +3142,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3202,7 +3217,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3218,6 +3233,11 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3255,10 +3275,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779298</v>
+        <v>122779265</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>90948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3271,42 +3291,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507119</v>
+        <v>507188</v>
       </c>
       <c r="R22" t="n">
-        <v>7053255</v>
+        <v>7053524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3341,17 +3360,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3360,6 +3375,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3370,14 +3390,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3395,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3411,30 +3426,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3442,13 +3453,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R23" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3482,7 +3493,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3497,32 +3508,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3540,10 +3546,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779265</v>
+        <v>122779272</v>
       </c>
       <c r="B24" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3556,21 +3562,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3587,13 +3593,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507188</v>
+        <v>507186</v>
       </c>
       <c r="R24" t="n">
-        <v>7053524</v>
+        <v>7053514</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3642,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3655,9 +3661,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3675,10 +3686,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779331</v>
+        <v>122779296</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3691,40 +3702,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507003</v>
+        <v>507257</v>
       </c>
       <c r="R25" t="n">
-        <v>7053201</v>
+        <v>7053479</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3758,7 +3774,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3767,33 +3783,17 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779282</v>
+        <v>122779318</v>
       </c>
       <c r="B26" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3823,25 +3823,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507098</v>
+        <v>507101</v>
       </c>
       <c r="R26" t="n">
-        <v>7053554</v>
+        <v>7053264</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779282</v>
+        <v>122779265</v>
       </c>
       <c r="B21" t="n">
-        <v>79883</v>
+        <v>90948</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,32 +3142,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3177,13 +3177,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507098</v>
+        <v>507188</v>
       </c>
       <c r="R21" t="n">
-        <v>7053554</v>
+        <v>7053524</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3213,11 +3213,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3237,27 +3232,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3275,10 +3265,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779265</v>
+        <v>122779282</v>
       </c>
       <c r="B22" t="n">
-        <v>90948</v>
+        <v>79883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3287,32 +3277,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3322,13 +3312,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507188</v>
+        <v>507098</v>
       </c>
       <c r="R22" t="n">
-        <v>7053524</v>
+        <v>7053554</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3358,6 +3348,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3377,22 +3372,27 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2704,7 +2704,7 @@
         <v>122779043</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779277</v>
+        <v>122779272</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>90973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,28 +2866,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507098</v>
+        <v>507186</v>
       </c>
       <c r="R19" t="n">
-        <v>7053554</v>
+        <v>7053514</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2935,11 +2935,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2955,24 +2950,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
         <v>122779298</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>122779265</v>
       </c>
       <c r="B21" t="n">
-        <v>90948</v>
+        <v>90951</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779282</v>
+        <v>122779296</v>
       </c>
       <c r="B22" t="n">
-        <v>79883</v>
+        <v>56683</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3277,45 +3277,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507098</v>
+        <v>507257</v>
       </c>
       <c r="R22" t="n">
-        <v>7053554</v>
+        <v>7053479</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3352,7 +3353,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3361,7 +3362,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3372,27 +3372,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3390,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779331</v>
+        <v>122779282</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79886</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3422,30 +3402,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3453,13 +3437,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507003</v>
+        <v>507098</v>
       </c>
       <c r="R23" t="n">
-        <v>7053201</v>
+        <v>7053554</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3493,7 +3477,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3508,27 +3492,32 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3546,10 +3535,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779272</v>
+        <v>122779277</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3562,28 +3551,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3593,10 +3582,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507186</v>
+        <v>507098</v>
       </c>
       <c r="R24" t="n">
-        <v>7053514</v>
+        <v>7053554</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3631,6 +3620,11 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3646,29 +3640,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3686,10 +3675,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779296</v>
+        <v>122779331</v>
       </c>
       <c r="B25" t="n">
-        <v>56680</v>
+        <v>78769</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3702,45 +3691,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507257</v>
+        <v>507003</v>
       </c>
       <c r="R25" t="n">
-        <v>7053479</v>
+        <v>7053201</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3774,7 +3758,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3783,17 +3767,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3814,7 +3814,7 @@
         <v>122779318</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779272</v>
+        <v>122779298</v>
       </c>
       <c r="B19" t="n">
-        <v>90973</v>
+        <v>57497</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,44 +2866,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507186</v>
+        <v>507119</v>
       </c>
       <c r="R19" t="n">
-        <v>7053514</v>
+        <v>7053255</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2935,13 +2936,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår i en gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2950,11 +2955,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779298</v>
+        <v>122779331</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,42 +3006,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507119</v>
+        <v>507003</v>
       </c>
       <c r="R20" t="n">
-        <v>7053255</v>
+        <v>7053201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,7 +3073,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3087,12 +3082,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3107,12 +3103,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3130,10 +3126,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779265</v>
+        <v>122779277</v>
       </c>
       <c r="B21" t="n">
-        <v>90951</v>
+        <v>79852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3146,28 +3142,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3177,13 +3173,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507188</v>
+        <v>507098</v>
       </c>
       <c r="R21" t="n">
-        <v>7053524</v>
+        <v>7053554</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3213,6 +3209,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3230,24 +3231,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3390,10 +3391,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779282</v>
+        <v>122779318</v>
       </c>
       <c r="B23" t="n">
-        <v>79886</v>
+        <v>79852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3402,25 +3403,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3437,10 +3438,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507098</v>
+        <v>507101</v>
       </c>
       <c r="R23" t="n">
-        <v>7053554</v>
+        <v>7053264</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3477,7 +3478,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3497,17 +3498,17 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gammal granskog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3517,7 +3518,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3535,10 +3536,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779277</v>
+        <v>122779265</v>
       </c>
       <c r="B24" t="n">
-        <v>79850</v>
+        <v>90953</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3551,28 +3552,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3582,13 +3583,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507098</v>
+        <v>507188</v>
       </c>
       <c r="R24" t="n">
-        <v>7053554</v>
+        <v>7053524</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3618,11 +3619,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3640,24 +3636,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3675,10 +3671,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779331</v>
+        <v>122779272</v>
       </c>
       <c r="B25" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3691,26 +3687,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507003</v>
+        <v>507186</v>
       </c>
       <c r="R25" t="n">
-        <v>7053201</v>
+        <v>7053514</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3754,11 +3754,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3773,7 +3768,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779318</v>
+        <v>122779282</v>
       </c>
       <c r="B26" t="n">
-        <v>79850</v>
+        <v>79888</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3823,25 +3823,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507101</v>
+        <v>507098</v>
       </c>
       <c r="R26" t="n">
-        <v>7053264</v>
+        <v>7053554</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779298</v>
+        <v>122779318</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>79853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,45 +2866,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507119</v>
+        <v>507101</v>
       </c>
       <c r="R19" t="n">
-        <v>7053255</v>
+        <v>7053264</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2947,6 +2946,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2955,24 +2955,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2990,10 +2995,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779331</v>
+        <v>122779272</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3006,26 +3011,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3033,13 +3042,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507003</v>
+        <v>507186</v>
       </c>
       <c r="R20" t="n">
-        <v>7053201</v>
+        <v>7053514</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3069,11 +3078,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3088,7 +3092,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3103,12 +3112,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3126,10 +3135,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779277</v>
+        <v>122779265</v>
       </c>
       <c r="B21" t="n">
-        <v>79852</v>
+        <v>90959</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,28 +3151,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3173,13 +3182,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507098</v>
+        <v>507188</v>
       </c>
       <c r="R21" t="n">
-        <v>7053554</v>
+        <v>7053524</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3209,11 +3218,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,24 +3235,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3266,10 +3270,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779296</v>
+        <v>122779277</v>
       </c>
       <c r="B22" t="n">
-        <v>56683</v>
+        <v>79853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3282,42 +3286,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507257</v>
+        <v>507098</v>
       </c>
       <c r="R22" t="n">
-        <v>7053479</v>
+        <v>7053554</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3354,7 +3357,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3363,6 +3366,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3371,9 +3375,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3391,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779318</v>
+        <v>122779296</v>
       </c>
       <c r="B23" t="n">
-        <v>79852</v>
+        <v>56683</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3407,41 +3426,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507101</v>
+        <v>507257</v>
       </c>
       <c r="R23" t="n">
-        <v>7053264</v>
+        <v>7053479</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3478,7 +3498,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3487,7 +3507,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3498,27 +3517,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3536,10 +3535,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779265</v>
+        <v>122779282</v>
       </c>
       <c r="B24" t="n">
-        <v>90953</v>
+        <v>79889</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3548,32 +3547,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3583,13 +3582,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507188</v>
+        <v>507098</v>
       </c>
       <c r="R24" t="n">
-        <v>7053524</v>
+        <v>7053554</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3619,6 +3618,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3638,22 +3642,27 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3671,10 +3680,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779272</v>
+        <v>122779331</v>
       </c>
       <c r="B25" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3687,30 +3696,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3718,13 +3723,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507186</v>
+        <v>507003</v>
       </c>
       <c r="R25" t="n">
-        <v>7053514</v>
+        <v>7053201</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3754,6 +3759,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3768,12 +3778,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3788,12 +3793,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3811,10 +3816,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779282</v>
+        <v>122779298</v>
       </c>
       <c r="B26" t="n">
-        <v>79888</v>
+        <v>57497</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3823,48 +3828,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507098</v>
+        <v>507119</v>
       </c>
       <c r="R26" t="n">
-        <v>7053554</v>
+        <v>7053255</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3898,7 +3904,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3907,7 +3913,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3916,29 +3921,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779318</v>
+        <v>122779331</v>
       </c>
       <c r="B19" t="n">
-        <v>79853</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2866,30 +2866,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2897,13 +2893,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507101</v>
+        <v>507003</v>
       </c>
       <c r="R19" t="n">
-        <v>7053264</v>
+        <v>7053201</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2937,7 +2933,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2952,32 +2948,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2998,7 +2989,7 @@
         <v>122779272</v>
       </c>
       <c r="B20" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3135,10 +3126,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779265</v>
+        <v>122779282</v>
       </c>
       <c r="B21" t="n">
-        <v>90959</v>
+        <v>79892</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3147,32 +3138,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3182,13 +3173,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507188</v>
+        <v>507098</v>
       </c>
       <c r="R21" t="n">
-        <v>7053524</v>
+        <v>7053554</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3218,6 +3209,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3237,22 +3233,27 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3270,10 +3271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779277</v>
+        <v>122779318</v>
       </c>
       <c r="B22" t="n">
-        <v>79853</v>
+        <v>79856</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3317,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507098</v>
+        <v>507101</v>
       </c>
       <c r="R22" t="n">
-        <v>7053554</v>
+        <v>7053264</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3357,7 +3358,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3375,14 +3376,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3392,7 +3398,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3416,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779296</v>
+        <v>122779265</v>
       </c>
       <c r="B23" t="n">
-        <v>56683</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3426,45 +3432,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507257</v>
+        <v>507188</v>
       </c>
       <c r="R23" t="n">
-        <v>7053479</v>
+        <v>7053524</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3496,17 +3501,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3517,7 +3518,22 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gammal grandominerad skog.</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3535,10 +3551,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779282</v>
+        <v>122779277</v>
       </c>
       <c r="B24" t="n">
-        <v>79889</v>
+        <v>79856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3547,25 +3563,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3622,7 +3638,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3638,11 +3654,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3680,10 +3691,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779331</v>
+        <v>122779296</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>56683</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3696,40 +3707,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507003</v>
+        <v>507257</v>
       </c>
       <c r="R25" t="n">
-        <v>7053201</v>
+        <v>7053479</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3763,7 +3779,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3772,33 +3788,17 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -4088,10 +4088,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123591258</v>
+        <v>123581420</v>
       </c>
       <c r="B28" t="n">
-        <v>100645</v>
+        <v>78775</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4100,46 +4100,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506882</v>
+        <v>507128</v>
       </c>
       <c r="R28" t="n">
-        <v>7053247</v>
+        <v>7053537</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4183,6 +4178,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4200,10 +4215,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123581420</v>
+        <v>123591258</v>
       </c>
       <c r="B29" t="n">
-        <v>78775</v>
+        <v>100645</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4212,41 +4227,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507128</v>
+        <v>506882</v>
       </c>
       <c r="R29" t="n">
-        <v>7053537</v>
+        <v>7053247</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4290,26 +4310,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123579984</v>
+        <v>123588776</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>79857</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5144,27 +5144,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507018</v>
+        <v>507044</v>
       </c>
       <c r="R36" t="n">
-        <v>7053429</v>
+        <v>7053321</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5211,6 +5211,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5227,22 +5232,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5260,10 +5265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123583184</v>
+        <v>123579984</v>
       </c>
       <c r="B37" t="n">
-        <v>78775</v>
+        <v>90962</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5276,34 +5281,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507077</v>
+        <v>507018</v>
       </c>
       <c r="R37" t="n">
-        <v>7053510</v>
+        <v>7053429</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5364,12 +5374,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5387,10 +5397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123588776</v>
+        <v>123583184</v>
       </c>
       <c r="B38" t="n">
-        <v>79857</v>
+        <v>78775</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5403,39 +5413,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507044</v>
+        <v>507077</v>
       </c>
       <c r="R38" t="n">
-        <v>7053321</v>
+        <v>7053510</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5470,11 +5475,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5491,22 +5491,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5935,7 +5935,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123587292</v>
+        <v>123583498</v>
       </c>
       <c r="B42" t="n">
         <v>78775</v>
@@ -5975,13 +5975,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507134</v>
+        <v>507170</v>
       </c>
       <c r="R42" t="n">
-        <v>7053449</v>
+        <v>7053530</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123583498</v>
+        <v>123583373</v>
       </c>
       <c r="B43" t="n">
         <v>78775</v>
@@ -6096,19 +6096,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507170</v>
+        <v>507115</v>
       </c>
       <c r="R43" t="n">
-        <v>7053530</v>
+        <v>7053507</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6166,12 +6171,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6189,7 +6194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123583373</v>
+        <v>123587292</v>
       </c>
       <c r="B44" t="n">
         <v>78775</v>
@@ -6223,24 +6228,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507115</v>
+        <v>507134</v>
       </c>
       <c r="R44" t="n">
-        <v>7053507</v>
+        <v>7053449</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123589530</v>
+        <v>123586447</v>
       </c>
       <c r="B50" t="n">
-        <v>97333</v>
+        <v>57634</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7003,46 +7003,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507044</v>
+        <v>507120</v>
       </c>
       <c r="R50" t="n">
-        <v>7053131</v>
+        <v>7053421</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7072,6 +7081,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7103,10 +7117,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123584458</v>
+        <v>123589530</v>
       </c>
       <c r="B51" t="n">
-        <v>91654</v>
+        <v>97333</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7119,27 +7133,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7148,13 +7162,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507220</v>
+        <v>507044</v>
       </c>
       <c r="R51" t="n">
-        <v>7053559</v>
+        <v>7053131</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7186,11 +7200,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7203,26 +7212,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7240,10 +7229,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123586447</v>
+        <v>123584458</v>
       </c>
       <c r="B52" t="n">
-        <v>57634</v>
+        <v>91654</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7252,55 +7241,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507120</v>
+        <v>507220</v>
       </c>
       <c r="R52" t="n">
-        <v>7053421</v>
+        <v>7053559</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7334,7 +7314,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7349,6 +7329,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123588546</v>
+        <v>123576626</v>
       </c>
       <c r="B54" t="n">
-        <v>57481</v>
+        <v>90984</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7509,32 +7509,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7543,13 +7538,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507024</v>
+        <v>506978</v>
       </c>
       <c r="R54" t="n">
-        <v>7053316</v>
+        <v>7053390</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7581,11 +7576,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7612,12 +7602,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7635,10 +7625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123576626</v>
+        <v>123588546</v>
       </c>
       <c r="B55" t="n">
-        <v>90984</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7651,27 +7641,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7680,13 +7675,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506978</v>
+        <v>507024</v>
       </c>
       <c r="R55" t="n">
-        <v>7053390</v>
+        <v>7053316</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7718,6 +7713,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7744,12 +7744,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7767,10 +7767,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123577590</v>
+        <v>123582759</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>90984</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7783,32 +7783,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7817,13 +7821,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506932</v>
+        <v>507054</v>
       </c>
       <c r="R56" t="n">
-        <v>7053304</v>
+        <v>7053507</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7853,11 +7857,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8041,10 +8040,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123579440</v>
+        <v>123577590</v>
       </c>
       <c r="B58" t="n">
-        <v>97333</v>
+        <v>57481</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8053,31 +8052,36 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8086,13 +8090,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507010</v>
+        <v>506932</v>
       </c>
       <c r="R58" t="n">
-        <v>7053401</v>
+        <v>7053304</v>
       </c>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8124,6 +8128,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8132,6 +8141,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -8148,10 +8182,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123582759</v>
+        <v>123579440</v>
       </c>
       <c r="B59" t="n">
-        <v>90984</v>
+        <v>97333</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8160,40 +8194,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8202,13 +8227,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507054</v>
+        <v>507010</v>
       </c>
       <c r="R59" t="n">
-        <v>7053507</v>
+        <v>7053401</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8248,31 +8273,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123577978</v>
+        <v>123577590</v>
       </c>
       <c r="B27" t="n">
-        <v>90984</v>
+        <v>57487</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3972,27 +3972,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4001,13 +4006,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506936</v>
+        <v>506932</v>
       </c>
       <c r="R27" t="n">
-        <v>7053351</v>
+        <v>7053304</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4039,6 +4044,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4065,12 +4075,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4088,10 +4098,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123581420</v>
+        <v>123580927</v>
       </c>
       <c r="B28" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4128,13 +4138,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507128</v>
+        <v>507115</v>
       </c>
       <c r="R28" t="n">
-        <v>7053537</v>
+        <v>7053483</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4215,10 +4225,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123591258</v>
+        <v>123582871</v>
       </c>
       <c r="B29" t="n">
-        <v>100645</v>
+        <v>78781</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4227,43 +4237,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506882</v>
+        <v>507066</v>
       </c>
       <c r="R29" t="n">
-        <v>7053247</v>
+        <v>7053479</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4310,6 +4315,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4327,10 +4352,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123590902</v>
+        <v>123585185</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4343,32 +4368,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4377,13 +4397,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506945</v>
+        <v>507197</v>
       </c>
       <c r="R30" t="n">
-        <v>7053117</v>
+        <v>7053490</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4415,11 +4435,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4446,12 +4461,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4469,10 +4484,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123587645</v>
+        <v>123577798</v>
       </c>
       <c r="B31" t="n">
-        <v>57851</v>
+        <v>79862</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4481,45 +4496,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4528,13 +4529,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507096</v>
+        <v>506927</v>
       </c>
       <c r="R31" t="n">
-        <v>7053337</v>
+        <v>7053299</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4566,11 +4567,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4583,6 +4579,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4600,10 +4616,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123582066</v>
+        <v>123576777</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4616,47 +4632,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507073</v>
+        <v>506942</v>
       </c>
       <c r="R32" t="n">
-        <v>7053530</v>
+        <v>7053366</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4690,7 +4696,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4709,22 +4715,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4742,10 +4748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123583252</v>
+        <v>123582066</v>
       </c>
       <c r="B33" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4758,27 +4764,32 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4787,13 +4798,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507086</v>
+        <v>507073</v>
       </c>
       <c r="R33" t="n">
-        <v>7053520</v>
+        <v>7053530</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4825,6 +4836,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4841,22 +4857,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4874,10 +4890,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123584853</v>
+        <v>123581420</v>
       </c>
       <c r="B34" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4914,13 +4930,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507238</v>
+        <v>507128</v>
       </c>
       <c r="R34" t="n">
-        <v>7053518</v>
+        <v>7053537</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5001,10 +5017,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123576556</v>
+        <v>123585102</v>
       </c>
       <c r="B35" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5041,13 +5057,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506963</v>
+        <v>507242</v>
       </c>
       <c r="R35" t="n">
-        <v>7053384</v>
+        <v>7053471</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5128,10 +5144,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123588776</v>
+        <v>123583373</v>
       </c>
       <c r="B36" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5144,27 +5160,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5173,13 +5189,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507044</v>
+        <v>507115</v>
       </c>
       <c r="R36" t="n">
-        <v>7053321</v>
+        <v>7053507</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5211,11 +5227,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5232,22 +5243,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5265,10 +5276,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123579984</v>
+        <v>123583184</v>
       </c>
       <c r="B37" t="n">
-        <v>90962</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5281,39 +5292,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507018</v>
+        <v>507077</v>
       </c>
       <c r="R37" t="n">
-        <v>7053429</v>
+        <v>7053510</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5374,12 +5380,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5397,10 +5403,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123583184</v>
+        <v>123580751</v>
       </c>
       <c r="B38" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5413,34 +5419,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507077</v>
+        <v>507106</v>
       </c>
       <c r="R38" t="n">
-        <v>7053510</v>
+        <v>7053481</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5475,6 +5491,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5501,12 +5522,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5524,10 +5545,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123590101</v>
+        <v>123590902</v>
       </c>
       <c r="B39" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5574,10 +5595,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507030</v>
+        <v>506945</v>
       </c>
       <c r="R39" t="n">
-        <v>7053146</v>
+        <v>7053117</v>
       </c>
       <c r="S39" t="n">
         <v>7</v>
@@ -5614,7 +5635,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5666,10 +5687,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123581252</v>
+        <v>123583252</v>
       </c>
       <c r="B40" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5711,13 +5732,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507113</v>
+        <v>507086</v>
       </c>
       <c r="R40" t="n">
-        <v>7053527</v>
+        <v>7053520</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5749,11 +5770,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5780,12 +5796,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5803,10 +5819,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123583817</v>
+        <v>123587645</v>
       </c>
       <c r="B41" t="n">
-        <v>78775</v>
+        <v>57857</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5815,31 +5831,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5848,13 +5878,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507164</v>
+        <v>507096</v>
       </c>
       <c r="R41" t="n">
-        <v>7053542</v>
+        <v>7053337</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5886,6 +5916,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5898,26 +5933,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5935,10 +5950,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123583498</v>
+        <v>123582759</v>
       </c>
       <c r="B42" t="n">
-        <v>78775</v>
+        <v>91001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5951,37 +5966,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507170</v>
+        <v>507054</v>
       </c>
       <c r="R42" t="n">
-        <v>7053530</v>
+        <v>7053507</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6039,12 +6068,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6062,10 +6091,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123583373</v>
+        <v>123579557</v>
       </c>
       <c r="B43" t="n">
-        <v>78775</v>
+        <v>100662</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6074,31 +6103,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6107,13 +6136,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507115</v>
+        <v>507035</v>
       </c>
       <c r="R43" t="n">
-        <v>7053507</v>
+        <v>7053385</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6153,31 +6182,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6194,10 +6198,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123587292</v>
+        <v>123583498</v>
       </c>
       <c r="B44" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6234,13 +6238,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507134</v>
+        <v>507170</v>
       </c>
       <c r="R44" t="n">
-        <v>7053449</v>
+        <v>7053530</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6298,12 +6302,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6321,10 +6325,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123585702</v>
+        <v>123586447</v>
       </c>
       <c r="B45" t="n">
-        <v>78775</v>
+        <v>57640</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6337,37 +6341,51 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507157</v>
+        <v>507120</v>
       </c>
       <c r="R45" t="n">
-        <v>7053405</v>
+        <v>7053421</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6401,7 +6419,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6416,26 +6434,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6456,7 +6454,7 @@
         <v>123579421</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6595,10 +6593,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123577656</v>
+        <v>123576823</v>
       </c>
       <c r="B47" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6607,41 +6605,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506944</v>
+        <v>506940</v>
       </c>
       <c r="R47" t="n">
-        <v>7053309</v>
+        <v>7053366</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6673,6 +6676,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6689,22 +6697,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6722,10 +6730,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123580927</v>
+        <v>123588776</v>
       </c>
       <c r="B48" t="n">
-        <v>78775</v>
+        <v>79863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6738,37 +6746,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507115</v>
+        <v>507044</v>
       </c>
       <c r="R48" t="n">
-        <v>7053483</v>
+        <v>7053321</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6800,6 +6813,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6816,22 +6834,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6849,10 +6867,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123580751</v>
+        <v>123588546</v>
       </c>
       <c r="B49" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6899,13 +6917,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507106</v>
+        <v>507024</v>
       </c>
       <c r="R49" t="n">
-        <v>7053481</v>
+        <v>7053316</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6939,7 +6957,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6991,10 +7009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123586447</v>
+        <v>123583817</v>
       </c>
       <c r="B50" t="n">
-        <v>57634</v>
+        <v>78781</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7007,51 +7025,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507120</v>
+        <v>507164</v>
       </c>
       <c r="R50" t="n">
-        <v>7053421</v>
+        <v>7053542</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7083,11 +7092,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -7100,6 +7104,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7117,10 +7141,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123589530</v>
+        <v>123577978</v>
       </c>
       <c r="B51" t="n">
-        <v>97333</v>
+        <v>91001</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7129,31 +7153,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7162,13 +7186,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507044</v>
+        <v>506936</v>
       </c>
       <c r="R51" t="n">
-        <v>7053131</v>
+        <v>7053351</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7212,6 +7236,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7229,10 +7273,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123584458</v>
+        <v>123585014</v>
       </c>
       <c r="B52" t="n">
-        <v>91654</v>
+        <v>91671</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7274,13 +7318,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507220</v>
+        <v>507278</v>
       </c>
       <c r="R52" t="n">
-        <v>7053559</v>
+        <v>7053515</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7312,11 +7356,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7343,12 +7382,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7366,10 +7405,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123582871</v>
+        <v>123590101</v>
       </c>
       <c r="B53" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7382,37 +7421,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507066</v>
+        <v>507030</v>
       </c>
       <c r="R53" t="n">
-        <v>7053479</v>
+        <v>7053146</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7444,6 +7493,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7470,12 +7524,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7493,10 +7547,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123576626</v>
+        <v>123586717</v>
       </c>
       <c r="B54" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7509,39 +7563,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506978</v>
+        <v>507076</v>
       </c>
       <c r="R54" t="n">
-        <v>7053390</v>
+        <v>7053414</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -7625,10 +7674,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123588546</v>
+        <v>123585702</v>
       </c>
       <c r="B55" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7641,47 +7690,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507024</v>
+        <v>507157</v>
       </c>
       <c r="R55" t="n">
-        <v>7053316</v>
+        <v>7053405</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7715,7 +7754,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7744,12 +7783,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7767,10 +7806,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123582759</v>
+        <v>123588146</v>
       </c>
       <c r="B56" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7783,51 +7822,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507054</v>
+        <v>507059</v>
       </c>
       <c r="R56" t="n">
-        <v>7053507</v>
+        <v>7053347</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7885,12 +7910,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7908,10 +7933,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123580416</v>
+        <v>123584458</v>
       </c>
       <c r="B57" t="n">
-        <v>90962</v>
+        <v>91671</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7920,25 +7945,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7953,13 +7978,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507047</v>
+        <v>507220</v>
       </c>
       <c r="R57" t="n">
-        <v>7053451</v>
+        <v>7053559</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7991,6 +8016,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8017,12 +8047,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8040,10 +8070,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123577590</v>
+        <v>123585385</v>
       </c>
       <c r="B58" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8056,32 +8086,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8090,13 +8115,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506932</v>
+        <v>507169</v>
       </c>
       <c r="R58" t="n">
-        <v>7053304</v>
+        <v>7053461</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8128,11 +8153,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8159,12 +8179,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8185,7 +8205,7 @@
         <v>123579440</v>
       </c>
       <c r="B59" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8289,10 +8309,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123591099</v>
+        <v>123589530</v>
       </c>
       <c r="B60" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8301,41 +8321,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506907</v>
+        <v>507044</v>
       </c>
       <c r="R60" t="n">
-        <v>7053220</v>
+        <v>7053131</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8379,26 +8404,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8416,10 +8421,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123585385</v>
+        <v>123581252</v>
       </c>
       <c r="B61" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8432,27 +8437,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8461,13 +8466,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507169</v>
+        <v>507113</v>
       </c>
       <c r="R61" t="n">
-        <v>7053461</v>
+        <v>7053527</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8499,6 +8504,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8515,22 +8525,22 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8548,10 +8558,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123585825</v>
+        <v>123576626</v>
       </c>
       <c r="B62" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8593,10 +8603,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507140</v>
+        <v>506978</v>
       </c>
       <c r="R62" t="n">
-        <v>7053422</v>
+        <v>7053390</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -8680,10 +8690,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123577798</v>
+        <v>123587292</v>
       </c>
       <c r="B63" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8696,42 +8706,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506927</v>
+        <v>507134</v>
       </c>
       <c r="R63" t="n">
-        <v>7053299</v>
+        <v>7053449</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8779,22 +8784,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8812,10 +8817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123576777</v>
+        <v>123591099</v>
       </c>
       <c r="B64" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8828,21 +8833,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8852,13 +8857,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506942</v>
+        <v>506907</v>
       </c>
       <c r="R64" t="n">
-        <v>7053366</v>
+        <v>7053220</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8890,11 +8895,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8911,22 +8911,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123585102</v>
+        <v>123576556</v>
       </c>
       <c r="B65" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8984,13 +8984,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507242</v>
+        <v>506963</v>
       </c>
       <c r="R65" t="n">
-        <v>7053471</v>
+        <v>7053384</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9071,10 +9071,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123576823</v>
+        <v>123584853</v>
       </c>
       <c r="B66" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9083,46 +9083,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506940</v>
+        <v>507238</v>
       </c>
       <c r="R66" t="n">
-        <v>7053366</v>
+        <v>7053518</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9154,11 +9149,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9175,22 +9165,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9208,10 +9198,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123585014</v>
+        <v>123585825</v>
       </c>
       <c r="B67" t="n">
-        <v>91654</v>
+        <v>91001</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9220,25 +9210,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9253,13 +9243,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507278</v>
+        <v>507140</v>
       </c>
       <c r="R67" t="n">
-        <v>7053515</v>
+        <v>7053422</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9340,10 +9330,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123585185</v>
+        <v>123591258</v>
       </c>
       <c r="B68" t="n">
-        <v>78775</v>
+        <v>100662</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9352,31 +9342,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9385,13 +9375,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507197</v>
+        <v>506882</v>
       </c>
       <c r="R68" t="n">
-        <v>7053490</v>
+        <v>7053247</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9435,26 +9425,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9472,10 +9442,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123588146</v>
+        <v>123589076</v>
       </c>
       <c r="B69" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9512,13 +9482,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507059</v>
+        <v>507050</v>
       </c>
       <c r="R69" t="n">
-        <v>7053347</v>
+        <v>7053220</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9599,10 +9569,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123589076</v>
+        <v>123577656</v>
       </c>
       <c r="B70" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9639,13 +9609,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507050</v>
+        <v>506944</v>
       </c>
       <c r="R70" t="n">
-        <v>7053220</v>
+        <v>7053309</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9726,10 +9696,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123579557</v>
+        <v>123580202</v>
       </c>
       <c r="B71" t="n">
-        <v>100645</v>
+        <v>79898</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9742,27 +9712,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9771,13 +9741,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507035</v>
+        <v>507014</v>
       </c>
       <c r="R71" t="n">
-        <v>7053385</v>
+        <v>7053440</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9817,6 +9787,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9833,10 +9828,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123586717</v>
+        <v>123579984</v>
       </c>
       <c r="B72" t="n">
-        <v>78775</v>
+        <v>90979</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9849,34 +9844,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507076</v>
+        <v>507018</v>
       </c>
       <c r="R72" t="n">
-        <v>7053414</v>
+        <v>7053429</v>
       </c>
       <c r="S72" t="n">
         <v>9</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123580202</v>
+        <v>123580416</v>
       </c>
       <c r="B73" t="n">
-        <v>79892</v>
+        <v>90979</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9972,31 +9972,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -10005,13 +10005,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507014</v>
+        <v>507047</v>
       </c>
       <c r="R73" t="n">
-        <v>7053440</v>
+        <v>7053451</v>
       </c>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10059,22 +10059,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123582066</v>
+        <v>123581420</v>
       </c>
       <c r="B33" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4764,47 +4764,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507073</v>
+        <v>507128</v>
       </c>
       <c r="R33" t="n">
-        <v>7053530</v>
+        <v>7053537</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4836,11 +4826,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4867,12 +4852,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4890,7 +4875,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123581420</v>
+        <v>123585102</v>
       </c>
       <c r="B34" t="n">
         <v>78781</v>
@@ -4930,13 +4915,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507128</v>
+        <v>507242</v>
       </c>
       <c r="R34" t="n">
-        <v>7053537</v>
+        <v>7053471</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5017,7 +5002,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123585102</v>
+        <v>123583373</v>
       </c>
       <c r="B35" t="n">
         <v>78781</v>
@@ -5051,19 +5036,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507242</v>
+        <v>507115</v>
       </c>
       <c r="R35" t="n">
-        <v>7053471</v>
+        <v>7053507</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5121,12 +5111,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5144,7 +5134,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123583373</v>
+        <v>123583184</v>
       </c>
       <c r="B36" t="n">
         <v>78781</v>
@@ -5178,24 +5168,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507115</v>
+        <v>507077</v>
       </c>
       <c r="R36" t="n">
-        <v>7053507</v>
+        <v>7053510</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5253,12 +5238,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5276,10 +5261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123583184</v>
+        <v>123583252</v>
       </c>
       <c r="B37" t="n">
-        <v>78781</v>
+        <v>79862</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5292,34 +5277,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507077</v>
+        <v>507086</v>
       </c>
       <c r="R37" t="n">
-        <v>7053510</v>
+        <v>7053520</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5370,22 +5360,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5403,10 +5393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123580751</v>
+        <v>123587645</v>
       </c>
       <c r="B38" t="n">
-        <v>57487</v>
+        <v>57857</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5415,20 +5405,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5436,10 +5426,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5453,13 +5452,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507106</v>
+        <v>507096</v>
       </c>
       <c r="R38" t="n">
-        <v>7053481</v>
+        <v>7053337</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5493,7 +5492,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5508,26 +5507,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5545,10 +5524,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123590902</v>
+        <v>123582759</v>
       </c>
       <c r="B39" t="n">
-        <v>57487</v>
+        <v>91001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5561,32 +5540,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5595,13 +5578,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506945</v>
+        <v>507054</v>
       </c>
       <c r="R39" t="n">
-        <v>7053117</v>
+        <v>7053507</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5631,11 +5614,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5687,10 +5665,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123583252</v>
+        <v>123579557</v>
       </c>
       <c r="B40" t="n">
-        <v>79862</v>
+        <v>100662</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5699,31 +5677,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5732,10 +5710,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507086</v>
+        <v>507035</v>
       </c>
       <c r="R40" t="n">
-        <v>7053520</v>
+        <v>7053385</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5778,31 +5756,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5819,10 +5772,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123587645</v>
+        <v>123583498</v>
       </c>
       <c r="B41" t="n">
-        <v>57857</v>
+        <v>78781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5831,60 +5784,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507096</v>
+        <v>507170</v>
       </c>
       <c r="R41" t="n">
-        <v>7053337</v>
+        <v>7053530</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5916,11 +5850,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5933,6 +5862,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5950,10 +5899,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123582759</v>
+        <v>123586447</v>
       </c>
       <c r="B42" t="n">
-        <v>91001</v>
+        <v>57640</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5966,51 +5915,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507054</v>
+        <v>507120</v>
       </c>
       <c r="R42" t="n">
-        <v>7053507</v>
+        <v>7053421</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6042,6 +5991,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6054,26 +6008,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6091,10 +6025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123579557</v>
+        <v>123576823</v>
       </c>
       <c r="B43" t="n">
-        <v>100662</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6107,27 +6041,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6136,13 +6070,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507035</v>
+        <v>506940</v>
       </c>
       <c r="R43" t="n">
-        <v>7053385</v>
+        <v>7053366</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6174,6 +6108,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6182,6 +6121,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6198,10 +6162,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123583498</v>
+        <v>123588776</v>
       </c>
       <c r="B44" t="n">
-        <v>78781</v>
+        <v>79863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6214,34 +6178,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507170</v>
+        <v>507044</v>
       </c>
       <c r="R44" t="n">
-        <v>7053530</v>
+        <v>7053321</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6276,6 +6245,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6292,22 +6266,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6325,10 +6299,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123586447</v>
+        <v>123583817</v>
       </c>
       <c r="B45" t="n">
-        <v>57640</v>
+        <v>78781</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6341,51 +6315,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507120</v>
+        <v>507164</v>
       </c>
       <c r="R45" t="n">
-        <v>7053421</v>
+        <v>7053542</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6417,11 +6382,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6434,6 +6394,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6451,10 +6431,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123579421</v>
+        <v>123577978</v>
       </c>
       <c r="B46" t="n">
-        <v>57487</v>
+        <v>91001</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6467,32 +6447,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6501,13 +6476,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507014</v>
+        <v>506936</v>
       </c>
       <c r="R46" t="n">
-        <v>7053420</v>
+        <v>7053351</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6539,11 +6514,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6570,12 +6540,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6593,10 +6563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123576823</v>
+        <v>123585014</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>91671</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6609,27 +6579,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6638,13 +6608,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506940</v>
+        <v>507278</v>
       </c>
       <c r="R47" t="n">
-        <v>7053366</v>
+        <v>7053515</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6676,11 +6646,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6697,22 +6662,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6730,10 +6695,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123588776</v>
+        <v>123586717</v>
       </c>
       <c r="B48" t="n">
-        <v>79863</v>
+        <v>78781</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6746,39 +6711,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507044</v>
+        <v>507076</v>
       </c>
       <c r="R48" t="n">
-        <v>7053321</v>
+        <v>7053414</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -6813,11 +6773,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6834,22 +6789,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6867,10 +6822,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123588546</v>
+        <v>123585702</v>
       </c>
       <c r="B49" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6883,47 +6838,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507024</v>
+        <v>507157</v>
       </c>
       <c r="R49" t="n">
-        <v>7053316</v>
+        <v>7053405</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6957,7 +6902,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6986,12 +6931,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7009,7 +6954,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123583817</v>
+        <v>123588146</v>
       </c>
       <c r="B50" t="n">
         <v>78781</v>
@@ -7043,21 +6988,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507164</v>
+        <v>507059</v>
       </c>
       <c r="R50" t="n">
-        <v>7053542</v>
+        <v>7053347</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -7141,10 +7081,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123577978</v>
+        <v>123584458</v>
       </c>
       <c r="B51" t="n">
-        <v>91001</v>
+        <v>91671</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7153,25 +7093,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7186,13 +7126,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506936</v>
+        <v>507220</v>
       </c>
       <c r="R51" t="n">
-        <v>7053351</v>
+        <v>7053559</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7224,6 +7164,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7250,12 +7195,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7273,10 +7218,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123585014</v>
+        <v>123585385</v>
       </c>
       <c r="B52" t="n">
-        <v>91671</v>
+        <v>78781</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7285,31 +7230,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7318,13 +7263,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507278</v>
+        <v>507169</v>
       </c>
       <c r="R52" t="n">
-        <v>7053515</v>
+        <v>7053461</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7382,12 +7327,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7405,10 +7350,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123590101</v>
+        <v>123579440</v>
       </c>
       <c r="B53" t="n">
-        <v>57487</v>
+        <v>97350</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7417,36 +7362,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7455,13 +7395,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507030</v>
+        <v>507010</v>
       </c>
       <c r="R53" t="n">
-        <v>7053146</v>
+        <v>7053401</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7493,11 +7433,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7506,31 +7441,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7547,10 +7457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123586717</v>
+        <v>123589530</v>
       </c>
       <c r="B54" t="n">
-        <v>78781</v>
+        <v>97350</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7559,41 +7469,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507076</v>
+        <v>507044</v>
       </c>
       <c r="R54" t="n">
-        <v>7053414</v>
+        <v>7053131</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7637,26 +7552,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7674,10 +7569,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123585702</v>
+        <v>123576626</v>
       </c>
       <c r="B55" t="n">
-        <v>78781</v>
+        <v>91001</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7690,34 +7585,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507157</v>
+        <v>506978</v>
       </c>
       <c r="R55" t="n">
-        <v>7053405</v>
+        <v>7053390</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -7752,11 +7652,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7783,12 +7678,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7806,7 +7701,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123588146</v>
+        <v>123587292</v>
       </c>
       <c r="B56" t="n">
         <v>78781</v>
@@ -7846,13 +7741,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507059</v>
+        <v>507134</v>
       </c>
       <c r="R56" t="n">
-        <v>7053347</v>
+        <v>7053449</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7933,10 +7828,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123584458</v>
+        <v>123591099</v>
       </c>
       <c r="B57" t="n">
-        <v>91671</v>
+        <v>78781</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7945,46 +7840,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507220</v>
+        <v>506907</v>
       </c>
       <c r="R57" t="n">
-        <v>7053559</v>
+        <v>7053220</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8016,11 +7906,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -8047,12 +7932,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8070,7 +7955,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123585385</v>
+        <v>123576556</v>
       </c>
       <c r="B58" t="n">
         <v>78781</v>
@@ -8104,24 +7989,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507169</v>
+        <v>506963</v>
       </c>
       <c r="R58" t="n">
-        <v>7053461</v>
+        <v>7053384</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8202,10 +8082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123579440</v>
+        <v>123584853</v>
       </c>
       <c r="B59" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8214,46 +8094,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507010</v>
+        <v>507238</v>
       </c>
       <c r="R59" t="n">
-        <v>7053401</v>
+        <v>7053518</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8293,6 +8168,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -8309,10 +8209,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123589530</v>
+        <v>123585825</v>
       </c>
       <c r="B60" t="n">
-        <v>97350</v>
+        <v>91001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8321,31 +8221,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8354,13 +8254,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507044</v>
+        <v>507140</v>
       </c>
       <c r="R60" t="n">
-        <v>7053131</v>
+        <v>7053422</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8404,6 +8304,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8421,10 +8341,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123581252</v>
+        <v>123591258</v>
       </c>
       <c r="B61" t="n">
-        <v>79862</v>
+        <v>100662</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8433,31 +8353,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8466,13 +8386,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507113</v>
+        <v>506882</v>
       </c>
       <c r="R61" t="n">
-        <v>7053527</v>
+        <v>7053247</v>
       </c>
       <c r="S61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8504,11 +8424,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -8521,26 +8436,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8558,10 +8453,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123576626</v>
+        <v>123589076</v>
       </c>
       <c r="B62" t="n">
-        <v>91001</v>
+        <v>78781</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8574,42 +8469,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506978</v>
+        <v>507050</v>
       </c>
       <c r="R62" t="n">
-        <v>7053390</v>
+        <v>7053220</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8667,12 +8557,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8690,7 +8580,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123587292</v>
+        <v>123577656</v>
       </c>
       <c r="B63" t="n">
         <v>78781</v>
@@ -8730,13 +8620,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507134</v>
+        <v>506944</v>
       </c>
       <c r="R63" t="n">
-        <v>7053449</v>
+        <v>7053309</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8817,10 +8707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123591099</v>
+        <v>123580202</v>
       </c>
       <c r="B64" t="n">
-        <v>78781</v>
+        <v>79898</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8829,41 +8719,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506907</v>
+        <v>507014</v>
       </c>
       <c r="R64" t="n">
-        <v>7053220</v>
+        <v>7053440</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8911,22 +8806,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8944,10 +8839,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123576556</v>
+        <v>123579984</v>
       </c>
       <c r="B65" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8960,37 +8855,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506963</v>
+        <v>507018</v>
       </c>
       <c r="R65" t="n">
-        <v>7053384</v>
+        <v>7053429</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9048,12 +8948,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9071,10 +8971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123584853</v>
+        <v>123580416</v>
       </c>
       <c r="B66" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9087,37 +8987,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507238</v>
+        <v>507047</v>
       </c>
       <c r="R66" t="n">
-        <v>7053518</v>
+        <v>7053451</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9175,12 +9080,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9198,10 +9103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123585825</v>
+        <v>123581252</v>
       </c>
       <c r="B67" t="n">
-        <v>91001</v>
+        <v>79862</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9214,27 +9119,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -9243,13 +9148,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507140</v>
+        <v>507113</v>
       </c>
       <c r="R67" t="n">
-        <v>7053422</v>
+        <v>7053527</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9281,6 +9186,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -9297,22 +9207,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9330,10 +9240,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123591258</v>
+        <v>123588546</v>
       </c>
       <c r="B68" t="n">
-        <v>100662</v>
+        <v>57487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9342,31 +9252,36 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9375,13 +9290,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506882</v>
+        <v>507024</v>
       </c>
       <c r="R68" t="n">
-        <v>7053247</v>
+        <v>7053316</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9413,6 +9328,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9425,6 +9345,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9442,10 +9382,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123589076</v>
+        <v>123580751</v>
       </c>
       <c r="B69" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9458,37 +9398,47 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507050</v>
+        <v>507106</v>
       </c>
       <c r="R69" t="n">
-        <v>7053220</v>
+        <v>7053481</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9520,6 +9470,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9546,12 +9501,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9569,10 +9524,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123577656</v>
+        <v>123590101</v>
       </c>
       <c r="B70" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9585,37 +9540,47 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506944</v>
+        <v>507030</v>
       </c>
       <c r="R70" t="n">
-        <v>7053309</v>
+        <v>7053146</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9647,6 +9612,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9673,12 +9643,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9696,10 +9666,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123580202</v>
+        <v>123579421</v>
       </c>
       <c r="B71" t="n">
-        <v>79898</v>
+        <v>57487</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9708,31 +9678,36 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9744,10 +9719,10 @@
         <v>507014</v>
       </c>
       <c r="R71" t="n">
-        <v>7053440</v>
+        <v>7053420</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9779,6 +9754,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9795,22 +9775,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9828,10 +9808,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123579984</v>
+        <v>123772770</v>
       </c>
       <c r="B72" t="n">
-        <v>90979</v>
+        <v>78781</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9844,42 +9824,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507018</v>
+        <v>507241</v>
       </c>
       <c r="R72" t="n">
-        <v>7053429</v>
+        <v>7053498</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9903,12 +9881,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9917,6 +9900,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9937,12 +9921,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9960,10 +9944,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123580416</v>
+        <v>123582066</v>
       </c>
       <c r="B73" t="n">
-        <v>90979</v>
+        <v>57487</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9976,27 +9960,32 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -10005,13 +9994,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507047</v>
+        <v>507073</v>
       </c>
       <c r="R73" t="n">
-        <v>7053451</v>
+        <v>7053530</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10041,6 +10030,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10089,6 +10083,288 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>123772501</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91001</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>507174</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7053322</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123590902</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57487</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>506945</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7053117</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -6025,10 +6025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123576823</v>
+        <v>123588776</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>79863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6037,31 +6037,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506940</v>
+        <v>507044</v>
       </c>
       <c r="R43" t="n">
-        <v>7053366</v>
+        <v>7053321</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På en grovbarkad sälglåga.</t>
+          <t>Enstaka bålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123588776</v>
+        <v>123576823</v>
       </c>
       <c r="B44" t="n">
-        <v>79863</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6174,31 +6174,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507044</v>
+        <v>506940</v>
       </c>
       <c r="R44" t="n">
-        <v>7053321</v>
+        <v>7053366</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
+          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -8453,10 +8453,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123589076</v>
+        <v>123579984</v>
       </c>
       <c r="B62" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8469,37 +8469,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507050</v>
+        <v>507018</v>
       </c>
       <c r="R62" t="n">
-        <v>7053220</v>
+        <v>7053429</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8557,12 +8562,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8580,10 +8585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123577656</v>
+        <v>123580416</v>
       </c>
       <c r="B63" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8596,37 +8601,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506944</v>
+        <v>507047</v>
       </c>
       <c r="R63" t="n">
-        <v>7053309</v>
+        <v>7053451</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8684,12 +8694,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8707,10 +8717,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123580202</v>
+        <v>123589076</v>
       </c>
       <c r="B64" t="n">
-        <v>79898</v>
+        <v>78781</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8719,46 +8729,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507014</v>
+        <v>507050</v>
       </c>
       <c r="R64" t="n">
-        <v>7053440</v>
+        <v>7053220</v>
       </c>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8806,22 +8811,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8839,10 +8844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123579984</v>
+        <v>123577656</v>
       </c>
       <c r="B65" t="n">
-        <v>90979</v>
+        <v>78781</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8855,39 +8860,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507018</v>
+        <v>506944</v>
       </c>
       <c r="R65" t="n">
-        <v>7053429</v>
+        <v>7053309</v>
       </c>
       <c r="S65" t="n">
         <v>9</v>
@@ -8948,12 +8948,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8971,10 +8971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123580416</v>
+        <v>123580202</v>
       </c>
       <c r="B66" t="n">
-        <v>90979</v>
+        <v>79898</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8983,31 +8983,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9016,13 +9016,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507047</v>
+        <v>507014</v>
       </c>
       <c r="R66" t="n">
-        <v>7053451</v>
+        <v>7053440</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9070,22 +9070,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -6025,10 +6025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123588776</v>
+        <v>123576823</v>
       </c>
       <c r="B43" t="n">
-        <v>79863</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6037,31 +6037,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507044</v>
+        <v>506940</v>
       </c>
       <c r="R43" t="n">
-        <v>7053321</v>
+        <v>7053366</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
+          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123576823</v>
+        <v>123588776</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>79863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6174,31 +6174,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506940</v>
+        <v>507044</v>
       </c>
       <c r="R44" t="n">
-        <v>7053366</v>
+        <v>7053321</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en grovbarkad sälglåga.</t>
+          <t>Enstaka bålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123584458</v>
+        <v>123585385</v>
       </c>
       <c r="B51" t="n">
-        <v>91671</v>
+        <v>78781</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7093,31 +7093,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507220</v>
+        <v>507169</v>
       </c>
       <c r="R51" t="n">
-        <v>7053559</v>
+        <v>7053461</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
@@ -7164,11 +7164,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7195,12 +7190,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7218,10 +7213,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123585385</v>
+        <v>123584458</v>
       </c>
       <c r="B52" t="n">
-        <v>78781</v>
+        <v>91671</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7230,31 +7225,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7263,10 +7258,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507169</v>
+        <v>507220</v>
       </c>
       <c r="R52" t="n">
-        <v>7053461</v>
+        <v>7053559</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -7301,6 +7296,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123577590</v>
+        <v>123580927</v>
       </c>
       <c r="B27" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3972,47 +3972,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506932</v>
+        <v>507115</v>
       </c>
       <c r="R27" t="n">
-        <v>7053304</v>
+        <v>7053483</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4044,11 +4034,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4075,12 +4060,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4098,10 +4083,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123580927</v>
+        <v>123577656</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4138,13 +4123,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507115</v>
+        <v>506944</v>
       </c>
       <c r="R28" t="n">
-        <v>7053483</v>
+        <v>7053309</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,10 +4210,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123582871</v>
+        <v>123577798</v>
       </c>
       <c r="B29" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4241,37 +4226,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507066</v>
+        <v>506927</v>
       </c>
       <c r="R29" t="n">
-        <v>7053479</v>
+        <v>7053299</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4319,22 +4309,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4352,10 +4342,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123585185</v>
+        <v>123581420</v>
       </c>
       <c r="B30" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4386,21 +4376,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507197</v>
+        <v>507128</v>
       </c>
       <c r="R30" t="n">
-        <v>7053490</v>
+        <v>7053537</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4484,10 +4469,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123577798</v>
+        <v>123585385</v>
       </c>
       <c r="B31" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4500,27 +4485,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4529,13 +4514,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506927</v>
+        <v>507169</v>
       </c>
       <c r="R31" t="n">
-        <v>7053299</v>
+        <v>7053461</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4583,22 +4568,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4616,10 +4601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123576777</v>
+        <v>123582871</v>
       </c>
       <c r="B32" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4632,21 +4617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4656,13 +4641,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506942</v>
+        <v>507066</v>
       </c>
       <c r="R32" t="n">
-        <v>7053366</v>
+        <v>7053479</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4694,11 +4679,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4715,22 +4695,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4748,10 +4728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123581420</v>
+        <v>123585702</v>
       </c>
       <c r="B33" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4788,10 +4768,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507128</v>
+        <v>507157</v>
       </c>
       <c r="R33" t="n">
-        <v>7053537</v>
+        <v>7053405</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4824,6 +4804,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4875,10 +4860,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123585102</v>
+        <v>123579440</v>
       </c>
       <c r="B34" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4887,41 +4872,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507242</v>
+        <v>507010</v>
       </c>
       <c r="R34" t="n">
-        <v>7053471</v>
+        <v>7053401</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4961,31 +4951,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -5002,10 +4967,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123583373</v>
+        <v>123584853</v>
       </c>
       <c r="B35" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5036,24 +5001,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507115</v>
+        <v>507238</v>
       </c>
       <c r="R35" t="n">
-        <v>7053507</v>
+        <v>7053518</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5111,12 +5071,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5134,10 +5094,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123583184</v>
+        <v>123589076</v>
       </c>
       <c r="B36" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5174,13 +5134,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507077</v>
+        <v>507050</v>
       </c>
       <c r="R36" t="n">
-        <v>7053510</v>
+        <v>7053220</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5261,10 +5221,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123583252</v>
+        <v>123586717</v>
       </c>
       <c r="B37" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5277,39 +5237,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507086</v>
+        <v>507076</v>
       </c>
       <c r="R37" t="n">
-        <v>7053520</v>
+        <v>7053414</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5360,22 +5315,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5393,10 +5348,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123587645</v>
+        <v>123583373</v>
       </c>
       <c r="B38" t="n">
-        <v>57857</v>
+        <v>78786</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5405,45 +5360,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5452,13 +5393,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507096</v>
+        <v>507115</v>
       </c>
       <c r="R38" t="n">
-        <v>7053337</v>
+        <v>7053507</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5490,11 +5431,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5507,6 +5443,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5524,10 +5480,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123582759</v>
+        <v>123585014</v>
       </c>
       <c r="B39" t="n">
-        <v>91001</v>
+        <v>91676</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5536,37 +5492,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -5578,13 +5525,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507054</v>
+        <v>507278</v>
       </c>
       <c r="R39" t="n">
-        <v>7053507</v>
+        <v>7053515</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5642,12 +5589,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5668,7 +5615,7 @@
         <v>123579557</v>
       </c>
       <c r="B40" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5772,10 +5719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123583498</v>
+        <v>123583252</v>
       </c>
       <c r="B41" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5788,34 +5735,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507170</v>
+        <v>507086</v>
       </c>
       <c r="R41" t="n">
-        <v>7053530</v>
+        <v>7053520</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5866,22 +5818,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5899,10 +5851,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123586447</v>
+        <v>123583817</v>
       </c>
       <c r="B42" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5915,51 +5867,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507120</v>
+        <v>507164</v>
       </c>
       <c r="R42" t="n">
-        <v>7053421</v>
+        <v>7053542</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5991,11 +5934,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6008,6 +5946,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6025,10 +5983,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123576823</v>
+        <v>123580202</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>79903</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6041,21 +5999,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6070,13 +6028,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506940</v>
+        <v>507014</v>
       </c>
       <c r="R43" t="n">
-        <v>7053366</v>
+        <v>7053440</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6108,11 +6066,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6139,12 +6092,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6162,10 +6115,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123588776</v>
+        <v>123582759</v>
       </c>
       <c r="B44" t="n">
-        <v>79863</v>
+        <v>91006</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6178,27 +6131,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6207,13 +6169,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507044</v>
+        <v>507054</v>
       </c>
       <c r="R44" t="n">
-        <v>7053321</v>
+        <v>7053507</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6245,11 +6207,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6266,22 +6223,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6299,10 +6256,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123583817</v>
+        <v>123576777</v>
       </c>
       <c r="B45" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6315,42 +6272,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507164</v>
+        <v>506942</v>
       </c>
       <c r="R45" t="n">
-        <v>7053542</v>
+        <v>7053366</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6382,6 +6334,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6398,22 +6355,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6431,10 +6388,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123577978</v>
+        <v>123583184</v>
       </c>
       <c r="B46" t="n">
-        <v>91001</v>
+        <v>78786</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6447,42 +6404,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506936</v>
+        <v>507077</v>
       </c>
       <c r="R46" t="n">
-        <v>7053351</v>
+        <v>7053510</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6540,12 +6492,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6563,10 +6515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123585014</v>
+        <v>123576556</v>
       </c>
       <c r="B47" t="n">
-        <v>91671</v>
+        <v>78786</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6575,46 +6527,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507278</v>
+        <v>506963</v>
       </c>
       <c r="R47" t="n">
-        <v>7053515</v>
+        <v>7053384</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6672,12 +6619,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6695,10 +6642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123586717</v>
+        <v>123576823</v>
       </c>
       <c r="B48" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6707,41 +6654,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507076</v>
+        <v>506940</v>
       </c>
       <c r="R48" t="n">
-        <v>7053414</v>
+        <v>7053366</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6773,6 +6725,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6789,22 +6746,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6822,10 +6779,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123585702</v>
+        <v>123586447</v>
       </c>
       <c r="B49" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6838,37 +6795,51 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507157</v>
+        <v>507120</v>
       </c>
       <c r="R49" t="n">
-        <v>7053405</v>
+        <v>7053421</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6902,7 +6873,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6917,26 +6888,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6954,10 +6905,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123588146</v>
+        <v>123587292</v>
       </c>
       <c r="B50" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6994,13 +6945,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507059</v>
+        <v>507134</v>
       </c>
       <c r="R50" t="n">
-        <v>7053347</v>
+        <v>7053449</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7081,10 +7032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123585385</v>
+        <v>123589530</v>
       </c>
       <c r="B51" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7093,31 +7044,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7126,13 +7077,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507169</v>
+        <v>507044</v>
       </c>
       <c r="R51" t="n">
-        <v>7053461</v>
+        <v>7053131</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7176,26 +7127,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7213,10 +7144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123584458</v>
+        <v>123580416</v>
       </c>
       <c r="B52" t="n">
-        <v>91671</v>
+        <v>90984</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7225,25 +7156,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7258,13 +7189,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507220</v>
+        <v>507047</v>
       </c>
       <c r="R52" t="n">
-        <v>7053559</v>
+        <v>7053451</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7296,11 +7227,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7327,12 +7253,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7350,10 +7276,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123579440</v>
+        <v>123585185</v>
       </c>
       <c r="B53" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7362,31 +7288,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7395,13 +7321,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507010</v>
+        <v>507197</v>
       </c>
       <c r="R53" t="n">
-        <v>7053401</v>
+        <v>7053490</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7441,6 +7367,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7457,10 +7408,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123589530</v>
+        <v>123585825</v>
       </c>
       <c r="B54" t="n">
-        <v>97350</v>
+        <v>91006</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7469,31 +7420,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7502,13 +7453,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507044</v>
+        <v>507140</v>
       </c>
       <c r="R54" t="n">
-        <v>7053131</v>
+        <v>7053422</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7552,6 +7503,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7569,10 +7540,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123576626</v>
+        <v>123583498</v>
       </c>
       <c r="B55" t="n">
-        <v>91001</v>
+        <v>78786</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7585,39 +7556,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506978</v>
+        <v>507170</v>
       </c>
       <c r="R55" t="n">
-        <v>7053390</v>
+        <v>7053530</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -7678,12 +7644,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7701,10 +7667,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123587292</v>
+        <v>123591099</v>
       </c>
       <c r="B56" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7741,13 +7707,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507134</v>
+        <v>506907</v>
       </c>
       <c r="R56" t="n">
-        <v>7053449</v>
+        <v>7053220</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7828,10 +7794,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123591099</v>
+        <v>123584458</v>
       </c>
       <c r="B57" t="n">
-        <v>78781</v>
+        <v>91676</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7840,41 +7806,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506907</v>
+        <v>507220</v>
       </c>
       <c r="R57" t="n">
-        <v>7053220</v>
+        <v>7053559</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7906,6 +7877,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7932,12 +7908,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7955,10 +7931,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123576556</v>
+        <v>123585102</v>
       </c>
       <c r="B58" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7995,13 +7971,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506963</v>
+        <v>507242</v>
       </c>
       <c r="R58" t="n">
-        <v>7053384</v>
+        <v>7053471</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8082,10 +8058,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123584853</v>
+        <v>123588146</v>
       </c>
       <c r="B59" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8122,13 +8098,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507238</v>
+        <v>507059</v>
       </c>
       <c r="R59" t="n">
-        <v>7053518</v>
+        <v>7053347</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8209,10 +8185,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123585825</v>
+        <v>123579984</v>
       </c>
       <c r="B60" t="n">
-        <v>91001</v>
+        <v>90984</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8225,21 +8201,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8254,10 +8230,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507140</v>
+        <v>507018</v>
       </c>
       <c r="R60" t="n">
-        <v>7053422</v>
+        <v>7053429</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -8344,7 +8320,7 @@
         <v>123591258</v>
       </c>
       <c r="B61" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8453,10 +8429,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123579984</v>
+        <v>123587645</v>
       </c>
       <c r="B62" t="n">
-        <v>90979</v>
+        <v>57860</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8465,31 +8441,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8498,13 +8488,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507018</v>
+        <v>507096</v>
       </c>
       <c r="R62" t="n">
-        <v>7053429</v>
+        <v>7053337</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8536,6 +8526,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8548,26 +8543,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8585,10 +8560,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123580416</v>
+        <v>123588776</v>
       </c>
       <c r="B63" t="n">
-        <v>90979</v>
+        <v>79868</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8601,27 +8576,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8630,13 +8605,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507047</v>
+        <v>507044</v>
       </c>
       <c r="R63" t="n">
-        <v>7053451</v>
+        <v>7053321</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8668,6 +8643,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8684,22 +8664,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8717,10 +8697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123589076</v>
+        <v>123577590</v>
       </c>
       <c r="B64" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8733,37 +8713,47 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507050</v>
+        <v>506932</v>
       </c>
       <c r="R64" t="n">
-        <v>7053220</v>
+        <v>7053304</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8795,6 +8785,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8821,12 +8816,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8844,10 +8839,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123577656</v>
+        <v>123576626</v>
       </c>
       <c r="B65" t="n">
-        <v>78781</v>
+        <v>91006</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8860,34 +8855,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506944</v>
+        <v>506978</v>
       </c>
       <c r="R65" t="n">
-        <v>7053309</v>
+        <v>7053390</v>
       </c>
       <c r="S65" t="n">
         <v>9</v>
@@ -8948,12 +8948,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8971,10 +8971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123580202</v>
+        <v>123577978</v>
       </c>
       <c r="B66" t="n">
-        <v>79898</v>
+        <v>91006</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8983,31 +8983,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9016,13 +9016,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507014</v>
+        <v>506936</v>
       </c>
       <c r="R66" t="n">
-        <v>7053440</v>
+        <v>7053351</v>
       </c>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9070,22 +9070,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123581252</v>
+        <v>123590101</v>
       </c>
       <c r="B67" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9119,27 +9119,32 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -9148,13 +9153,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507113</v>
+        <v>507030</v>
       </c>
       <c r="R67" t="n">
-        <v>7053527</v>
+        <v>7053146</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9188,7 +9193,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9207,22 +9212,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9240,10 +9245,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123588546</v>
+        <v>123590902</v>
       </c>
       <c r="B68" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9276,7 +9281,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9290,13 +9295,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507024</v>
+        <v>506945</v>
       </c>
       <c r="R68" t="n">
-        <v>7053316</v>
+        <v>7053117</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9330,7 +9335,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9385,7 +9390,7 @@
         <v>123580751</v>
       </c>
       <c r="B69" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9524,10 +9529,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123590101</v>
+        <v>123772770</v>
       </c>
       <c r="B70" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9540,47 +9545,40 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507030</v>
+        <v>507241</v>
       </c>
       <c r="R70" t="n">
-        <v>7053146</v>
+        <v>7053498</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9604,17 +9602,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9623,6 +9621,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9643,12 +9642,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9666,10 +9665,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123579421</v>
+        <v>123581252</v>
       </c>
       <c r="B71" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9682,32 +9681,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9716,13 +9710,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507014</v>
+        <v>507113</v>
       </c>
       <c r="R71" t="n">
-        <v>7053420</v>
+        <v>7053527</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9756,7 +9750,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9775,22 +9769,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9808,10 +9802,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123772770</v>
+        <v>123579421</v>
       </c>
       <c r="B72" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9824,40 +9818,47 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507241</v>
+        <v>507014</v>
       </c>
       <c r="R72" t="n">
-        <v>7053498</v>
+        <v>7053420</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9881,17 +9882,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9900,7 +9901,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9921,12 +9921,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123582066</v>
+        <v>123588546</v>
       </c>
       <c r="B73" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9994,13 +9994,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507073</v>
+        <v>507024</v>
       </c>
       <c r="R73" t="n">
-        <v>7053530</v>
+        <v>7053316</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10086,10 +10086,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123772501</v>
+        <v>123582066</v>
       </c>
       <c r="B74" t="n">
-        <v>91001</v>
+        <v>57490</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10102,44 +10102,47 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507174</v>
+        <v>507073</v>
       </c>
       <c r="R74" t="n">
-        <v>7053322</v>
+        <v>7053530</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10163,12 +10166,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10177,7 +10185,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10186,11 +10193,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ74" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10203,12 +10205,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10226,10 +10228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123590902</v>
+        <v>123772501</v>
       </c>
       <c r="B75" t="n">
-        <v>57487</v>
+        <v>91006</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10242,47 +10244,44 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506945</v>
+        <v>507174</v>
       </c>
       <c r="R75" t="n">
-        <v>7053117</v>
+        <v>7053322</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10306,17 +10305,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10325,6 +10319,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10333,6 +10328,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ75" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10345,12 +10345,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123580927</v>
+        <v>123577590</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3972,37 +3972,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507115</v>
+        <v>506932</v>
       </c>
       <c r="R27" t="n">
-        <v>7053483</v>
+        <v>7053304</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4034,6 +4044,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4060,12 +4075,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4086,7 +4101,7 @@
         <v>123577656</v>
       </c>
       <c r="B28" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4210,10 +4225,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123577798</v>
+        <v>123585385</v>
       </c>
       <c r="B29" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4226,27 +4241,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4255,13 +4270,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506927</v>
+        <v>507169</v>
       </c>
       <c r="R29" t="n">
-        <v>7053299</v>
+        <v>7053461</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4309,22 +4324,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4342,10 +4357,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123581420</v>
+        <v>123576777</v>
       </c>
       <c r="B30" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4358,21 +4373,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4382,13 +4397,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507128</v>
+        <v>506942</v>
       </c>
       <c r="R30" t="n">
-        <v>7053537</v>
+        <v>7053366</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4420,6 +4435,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4436,22 +4456,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4469,10 +4489,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123585385</v>
+        <v>123588776</v>
       </c>
       <c r="B31" t="n">
-        <v>78786</v>
+        <v>79870</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4485,27 +4505,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4514,13 +4534,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507169</v>
+        <v>507044</v>
       </c>
       <c r="R31" t="n">
-        <v>7053461</v>
+        <v>7053321</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4552,6 +4572,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4568,22 +4593,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4601,10 +4626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123582871</v>
+        <v>123587292</v>
       </c>
       <c r="B32" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4641,10 +4666,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507066</v>
+        <v>507134</v>
       </c>
       <c r="R32" t="n">
-        <v>7053479</v>
+        <v>7053449</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4728,10 +4753,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123585702</v>
+        <v>123587645</v>
       </c>
       <c r="B33" t="n">
-        <v>78786</v>
+        <v>57861</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4740,41 +4765,60 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507157</v>
+        <v>507096</v>
       </c>
       <c r="R33" t="n">
-        <v>7053405</v>
+        <v>7053337</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4808,7 +4852,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4823,26 +4867,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4860,10 +4884,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123579440</v>
+        <v>123580416</v>
       </c>
       <c r="B34" t="n">
-        <v>97367</v>
+        <v>90986</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4872,31 +4896,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4905,13 +4929,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507010</v>
+        <v>507047</v>
       </c>
       <c r="R34" t="n">
-        <v>7053401</v>
+        <v>7053451</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4951,6 +4975,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4967,10 +5016,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123584853</v>
+        <v>123591099</v>
       </c>
       <c r="B35" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5007,13 +5056,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507238</v>
+        <v>506907</v>
       </c>
       <c r="R35" t="n">
-        <v>7053518</v>
+        <v>7053220</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5094,10 +5143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123589076</v>
+        <v>123583252</v>
       </c>
       <c r="B36" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5110,37 +5159,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507050</v>
+        <v>507086</v>
       </c>
       <c r="R36" t="n">
-        <v>7053220</v>
+        <v>7053520</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5188,22 +5242,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5221,10 +5275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123586717</v>
+        <v>123585825</v>
       </c>
       <c r="B37" t="n">
-        <v>78786</v>
+        <v>91008</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5237,34 +5291,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507076</v>
+        <v>507140</v>
       </c>
       <c r="R37" t="n">
-        <v>7053414</v>
+        <v>7053422</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5348,10 +5407,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123583373</v>
+        <v>123579557</v>
       </c>
       <c r="B38" t="n">
-        <v>78786</v>
+        <v>100682</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5360,31 +5419,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5393,13 +5452,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507115</v>
+        <v>507035</v>
       </c>
       <c r="R38" t="n">
-        <v>7053507</v>
+        <v>7053385</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5439,31 +5498,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5480,10 +5514,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123585014</v>
+        <v>123581420</v>
       </c>
       <c r="B39" t="n">
-        <v>91676</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5492,46 +5526,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507278</v>
+        <v>507128</v>
       </c>
       <c r="R39" t="n">
-        <v>7053515</v>
+        <v>7053537</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5589,12 +5618,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5612,10 +5641,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123579557</v>
+        <v>123582759</v>
       </c>
       <c r="B40" t="n">
-        <v>100680</v>
+        <v>91008</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5624,31 +5653,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5657,13 +5695,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507035</v>
+        <v>507054</v>
       </c>
       <c r="R40" t="n">
-        <v>7053385</v>
+        <v>7053507</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5703,6 +5741,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5719,10 +5782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123583252</v>
+        <v>123576556</v>
       </c>
       <c r="B41" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5735,42 +5798,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507086</v>
+        <v>506963</v>
       </c>
       <c r="R41" t="n">
-        <v>7053520</v>
+        <v>7053384</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5818,22 +5876,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5851,10 +5909,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123583817</v>
+        <v>123580927</v>
       </c>
       <c r="B42" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5885,24 +5943,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507164</v>
+        <v>507115</v>
       </c>
       <c r="R42" t="n">
-        <v>7053542</v>
+        <v>7053483</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5983,10 +6036,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123580202</v>
+        <v>123582871</v>
       </c>
       <c r="B43" t="n">
-        <v>79903</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5995,46 +6048,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507014</v>
+        <v>507066</v>
       </c>
       <c r="R43" t="n">
-        <v>7053440</v>
+        <v>7053479</v>
       </c>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6082,22 +6130,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6115,10 +6163,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123582759</v>
+        <v>123583373</v>
       </c>
       <c r="B44" t="n">
-        <v>91006</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6131,36 +6179,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6169,13 +6208,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507054</v>
+        <v>507115</v>
       </c>
       <c r="R44" t="n">
         <v>7053507</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6233,12 +6272,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6256,10 +6295,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123576777</v>
+        <v>123577798</v>
       </c>
       <c r="B45" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6290,19 +6329,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506942</v>
+        <v>506927</v>
       </c>
       <c r="R45" t="n">
-        <v>7053366</v>
+        <v>7053299</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6334,11 +6378,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6365,12 +6404,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6388,10 +6427,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123583184</v>
+        <v>123576823</v>
       </c>
       <c r="B46" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6400,41 +6439,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507077</v>
+        <v>506940</v>
       </c>
       <c r="R46" t="n">
-        <v>7053510</v>
+        <v>7053366</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6466,6 +6510,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6482,22 +6531,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6515,10 +6564,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123576556</v>
+        <v>123589530</v>
       </c>
       <c r="B47" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6527,41 +6576,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506963</v>
+        <v>507044</v>
       </c>
       <c r="R47" t="n">
-        <v>7053384</v>
+        <v>7053131</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6605,26 +6659,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6642,10 +6676,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123576823</v>
+        <v>123579984</v>
       </c>
       <c r="B48" t="n">
-        <v>79896</v>
+        <v>90986</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6654,31 +6688,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6687,13 +6721,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506940</v>
+        <v>507018</v>
       </c>
       <c r="R48" t="n">
-        <v>7053366</v>
+        <v>7053429</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6725,11 +6759,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6746,22 +6775,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6779,10 +6808,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123586447</v>
+        <v>123585702</v>
       </c>
       <c r="B49" t="n">
-        <v>57643</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6795,51 +6824,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507120</v>
+        <v>507157</v>
       </c>
       <c r="R49" t="n">
-        <v>7053421</v>
+        <v>7053405</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6873,7 +6888,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6888,6 +6903,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6905,10 +6940,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123587292</v>
+        <v>123579440</v>
       </c>
       <c r="B50" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6917,41 +6952,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507134</v>
+        <v>507010</v>
       </c>
       <c r="R50" t="n">
-        <v>7053449</v>
+        <v>7053401</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6991,31 +7031,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7032,10 +7047,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123589530</v>
+        <v>123584853</v>
       </c>
       <c r="B51" t="n">
-        <v>97367</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7044,46 +7059,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507044</v>
+        <v>507238</v>
       </c>
       <c r="R51" t="n">
-        <v>7053131</v>
+        <v>7053518</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7127,6 +7137,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7144,10 +7174,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123580416</v>
+        <v>123583498</v>
       </c>
       <c r="B52" t="n">
-        <v>90984</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7160,42 +7190,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507047</v>
+        <v>507170</v>
       </c>
       <c r="R52" t="n">
-        <v>7053451</v>
+        <v>7053530</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7253,12 +7278,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7276,10 +7301,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123585185</v>
+        <v>123588146</v>
       </c>
       <c r="B53" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7310,21 +7335,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507197</v>
+        <v>507059</v>
       </c>
       <c r="R53" t="n">
-        <v>7053490</v>
+        <v>7053347</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -7408,10 +7428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123585825</v>
+        <v>123576626</v>
       </c>
       <c r="B54" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7453,10 +7473,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507140</v>
+        <v>506978</v>
       </c>
       <c r="R54" t="n">
-        <v>7053422</v>
+        <v>7053390</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -7540,10 +7560,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123583498</v>
+        <v>123580202</v>
       </c>
       <c r="B55" t="n">
-        <v>78786</v>
+        <v>79905</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7552,41 +7572,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507170</v>
+        <v>507014</v>
       </c>
       <c r="R55" t="n">
-        <v>7053530</v>
+        <v>7053440</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7634,22 +7659,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7667,10 +7692,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123591099</v>
+        <v>123589076</v>
       </c>
       <c r="B56" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7707,13 +7732,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506907</v>
+        <v>507050</v>
       </c>
       <c r="R56" t="n">
         <v>7053220</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7794,10 +7819,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123584458</v>
+        <v>123583817</v>
       </c>
       <c r="B57" t="n">
-        <v>91676</v>
+        <v>78788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7806,31 +7831,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7839,13 +7864,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507220</v>
+        <v>507164</v>
       </c>
       <c r="R57" t="n">
-        <v>7053559</v>
+        <v>7053542</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7877,11 +7902,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7908,12 +7928,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7931,10 +7951,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123585102</v>
+        <v>123577978</v>
       </c>
       <c r="B58" t="n">
-        <v>78786</v>
+        <v>91008</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7947,37 +7967,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507242</v>
+        <v>506936</v>
       </c>
       <c r="R58" t="n">
-        <v>7053471</v>
+        <v>7053351</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8035,12 +8060,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8058,10 +8083,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123588146</v>
+        <v>123585185</v>
       </c>
       <c r="B59" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8092,16 +8117,21 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507059</v>
+        <v>507197</v>
       </c>
       <c r="R59" t="n">
-        <v>7053347</v>
+        <v>7053490</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -8185,10 +8215,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123579984</v>
+        <v>123583184</v>
       </c>
       <c r="B60" t="n">
-        <v>90984</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8201,39 +8231,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507018</v>
+        <v>507077</v>
       </c>
       <c r="R60" t="n">
-        <v>7053429</v>
+        <v>7053510</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -8294,12 +8319,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8320,7 +8345,7 @@
         <v>123591258</v>
       </c>
       <c r="B61" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8429,10 +8454,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123587645</v>
+        <v>123585102</v>
       </c>
       <c r="B62" t="n">
-        <v>57860</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8441,57 +8466,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507096</v>
+        <v>507242</v>
       </c>
       <c r="R62" t="n">
-        <v>7053337</v>
+        <v>7053471</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8526,11 +8532,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8543,6 +8544,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8560,10 +8581,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123588776</v>
+        <v>123586717</v>
       </c>
       <c r="B63" t="n">
-        <v>79868</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8576,39 +8597,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507044</v>
+        <v>507076</v>
       </c>
       <c r="R63" t="n">
-        <v>7053321</v>
+        <v>7053414</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -8643,11 +8659,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8664,22 +8675,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8697,10 +8708,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123577590</v>
+        <v>123584458</v>
       </c>
       <c r="B64" t="n">
-        <v>57490</v>
+        <v>91678</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8709,36 +8720,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8747,13 +8753,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506932</v>
+        <v>507220</v>
       </c>
       <c r="R64" t="n">
-        <v>7053304</v>
+        <v>7053559</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8787,7 +8793,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8816,12 +8822,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8839,10 +8845,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123576626</v>
+        <v>123585014</v>
       </c>
       <c r="B65" t="n">
-        <v>91006</v>
+        <v>91678</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8851,25 +8857,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8884,13 +8890,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506978</v>
+        <v>507278</v>
       </c>
       <c r="R65" t="n">
-        <v>7053390</v>
+        <v>7053515</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8971,10 +8977,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123577978</v>
+        <v>123586447</v>
       </c>
       <c r="B66" t="n">
-        <v>91006</v>
+        <v>57644</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8987,42 +8993,51 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506936</v>
+        <v>507120</v>
       </c>
       <c r="R66" t="n">
-        <v>7053351</v>
+        <v>7053421</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9054,6 +9069,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9066,26 +9086,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9106,7 +9106,7 @@
         <v>123590101</v>
       </c>
       <c r="B67" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123590902</v>
+        <v>123588546</v>
       </c>
       <c r="B68" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9295,13 +9295,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506945</v>
+        <v>507024</v>
       </c>
       <c r="R68" t="n">
-        <v>7053117</v>
+        <v>7053316</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9387,10 +9387,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123580751</v>
+        <v>123579421</v>
       </c>
       <c r="B69" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507106</v>
+        <v>507014</v>
       </c>
       <c r="R69" t="n">
-        <v>7053481</v>
+        <v>7053420</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9529,10 +9529,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123772770</v>
+        <v>123580751</v>
       </c>
       <c r="B70" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9545,40 +9545,47 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507241</v>
+        <v>507106</v>
       </c>
       <c r="R70" t="n">
-        <v>7053498</v>
+        <v>7053481</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9602,17 +9609,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9621,7 +9628,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9642,12 +9648,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9665,10 +9671,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123581252</v>
+        <v>123590902</v>
       </c>
       <c r="B71" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9681,27 +9687,32 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9710,13 +9721,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507113</v>
+        <v>506945</v>
       </c>
       <c r="R71" t="n">
-        <v>7053527</v>
+        <v>7053117</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9750,7 +9761,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9769,22 +9780,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9802,10 +9813,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123579421</v>
+        <v>123772770</v>
       </c>
       <c r="B72" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9818,47 +9829,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507014</v>
+        <v>507241</v>
       </c>
       <c r="R72" t="n">
-        <v>7053420</v>
+        <v>7053498</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9882,17 +9886,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9901,6 +9905,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9921,12 +9926,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9944,10 +9949,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123588546</v>
+        <v>123772501</v>
       </c>
       <c r="B73" t="n">
-        <v>57490</v>
+        <v>91008</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9960,44 +9965,41 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507024</v>
+        <v>507174</v>
       </c>
       <c r="R73" t="n">
-        <v>7053316</v>
+        <v>7053322</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10024,17 +10026,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10043,6 +10040,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10051,6 +10049,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ73" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10063,12 +10066,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10086,10 +10089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123582066</v>
+        <v>123581252</v>
       </c>
       <c r="B74" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10102,32 +10105,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -10136,13 +10134,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507073</v>
+        <v>507113</v>
       </c>
       <c r="R74" t="n">
-        <v>7053530</v>
+        <v>7053527</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10176,7 +10174,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10195,22 +10193,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10228,10 +10226,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123772501</v>
+        <v>123582066</v>
       </c>
       <c r="B75" t="n">
-        <v>91006</v>
+        <v>57491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10244,44 +10242,47 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507174</v>
+        <v>507073</v>
       </c>
       <c r="R75" t="n">
-        <v>7053322</v>
+        <v>7053530</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10305,12 +10306,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10319,7 +10325,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10328,11 +10333,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ75" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10345,12 +10345,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -8454,10 +8454,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123585102</v>
+        <v>123586447</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8470,37 +8470,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507242</v>
+        <v>507120</v>
       </c>
       <c r="R62" t="n">
-        <v>7053471</v>
+        <v>7053421</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8532,6 +8546,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8544,26 +8563,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8581,7 +8580,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123586717</v>
+        <v>123585102</v>
       </c>
       <c r="B63" t="n">
         <v>78788</v>
@@ -8621,13 +8620,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507076</v>
+        <v>507242</v>
       </c>
       <c r="R63" t="n">
-        <v>7053414</v>
+        <v>7053471</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8685,12 +8684,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8708,10 +8707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123584458</v>
+        <v>123586717</v>
       </c>
       <c r="B64" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8720,46 +8719,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507220</v>
+        <v>507076</v>
       </c>
       <c r="R64" t="n">
-        <v>7053559</v>
+        <v>7053414</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8791,11 +8785,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8822,12 +8811,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8845,7 +8834,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123585014</v>
+        <v>123584458</v>
       </c>
       <c r="B65" t="n">
         <v>91678</v>
@@ -8890,13 +8879,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507278</v>
+        <v>507220</v>
       </c>
       <c r="R65" t="n">
-        <v>7053515</v>
+        <v>7053559</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8928,6 +8917,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8954,12 +8948,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8977,10 +8971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123586447</v>
+        <v>123585014</v>
       </c>
       <c r="B66" t="n">
-        <v>57644</v>
+        <v>91678</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8989,52 +8983,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507120</v>
+        <v>507278</v>
       </c>
       <c r="R66" t="n">
-        <v>7053421</v>
+        <v>7053515</v>
       </c>
       <c r="S66" t="n">
         <v>7</v>
@@ -9069,11 +9054,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9086,6 +9066,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -8083,10 +8083,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123585185</v>
+        <v>123591258</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>100682</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8095,31 +8095,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8128,13 +8128,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507197</v>
+        <v>506882</v>
       </c>
       <c r="R59" t="n">
-        <v>7053490</v>
+        <v>7053247</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8178,26 +8178,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8215,7 +8195,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123583184</v>
+        <v>123585185</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -8249,16 +8229,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507077</v>
+        <v>507197</v>
       </c>
       <c r="R60" t="n">
-        <v>7053510</v>
+        <v>7053490</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -8342,10 +8327,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123591258</v>
+        <v>123583184</v>
       </c>
       <c r="B61" t="n">
-        <v>100682</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8354,46 +8339,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506882</v>
+        <v>507077</v>
       </c>
       <c r="R61" t="n">
-        <v>7053247</v>
+        <v>7053510</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8437,6 +8417,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123585102</v>
+        <v>123584458</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8592,41 +8592,46 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507242</v>
+        <v>507220</v>
       </c>
       <c r="R63" t="n">
-        <v>7053471</v>
+        <v>7053559</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8658,6 +8663,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8684,12 +8694,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8707,10 +8717,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123586717</v>
+        <v>123585014</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8719,41 +8729,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507076</v>
+        <v>507278</v>
       </c>
       <c r="R64" t="n">
-        <v>7053414</v>
+        <v>7053515</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8834,10 +8849,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123584458</v>
+        <v>123585102</v>
       </c>
       <c r="B65" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8846,46 +8861,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507220</v>
+        <v>507242</v>
       </c>
       <c r="R65" t="n">
-        <v>7053559</v>
+        <v>7053471</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8917,11 +8927,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8948,12 +8953,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8971,10 +8976,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123585014</v>
+        <v>123586717</v>
       </c>
       <c r="B66" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8983,46 +8988,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507278</v>
+        <v>507076</v>
       </c>
       <c r="R66" t="n">
-        <v>7053515</v>
+        <v>7053414</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123577590</v>
+        <v>123588776</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
+        <v>79870</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3972,32 +3972,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4006,13 +4001,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506932</v>
+        <v>507044</v>
       </c>
       <c r="R27" t="n">
-        <v>7053304</v>
+        <v>7053321</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4046,7 +4041,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+          <t>Enstaka bålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4065,22 +4060,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4098,7 +4093,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123577656</v>
+        <v>123589076</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -4138,13 +4133,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506944</v>
+        <v>507050</v>
       </c>
       <c r="R28" t="n">
-        <v>7053309</v>
+        <v>7053220</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4225,7 +4220,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123585385</v>
+        <v>123577656</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -4259,24 +4254,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507169</v>
+        <v>506944</v>
       </c>
       <c r="R29" t="n">
-        <v>7053461</v>
+        <v>7053309</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4357,10 +4347,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123576777</v>
+        <v>123583373</v>
       </c>
       <c r="B30" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4373,37 +4363,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506942</v>
+        <v>507115</v>
       </c>
       <c r="R30" t="n">
-        <v>7053366</v>
+        <v>7053507</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4435,11 +4430,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4456,22 +4446,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4489,10 +4479,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123588776</v>
+        <v>123585825</v>
       </c>
       <c r="B31" t="n">
-        <v>79870</v>
+        <v>91008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4505,27 +4495,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4534,10 +4524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507044</v>
+        <v>507140</v>
       </c>
       <c r="R31" t="n">
-        <v>7053321</v>
+        <v>7053422</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4572,11 +4562,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4593,22 +4578,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4626,7 +4611,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123587292</v>
+        <v>123582871</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -4666,10 +4651,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507134</v>
+        <v>507066</v>
       </c>
       <c r="R32" t="n">
-        <v>7053449</v>
+        <v>7053479</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4753,10 +4738,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123587645</v>
+        <v>123585385</v>
       </c>
       <c r="B33" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4765,45 +4750,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4812,13 +4783,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507096</v>
+        <v>507169</v>
       </c>
       <c r="R33" t="n">
-        <v>7053337</v>
+        <v>7053461</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4850,11 +4821,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4867,6 +4833,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4884,10 +4870,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123580416</v>
+        <v>123585014</v>
       </c>
       <c r="B34" t="n">
-        <v>90986</v>
+        <v>91678</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4896,25 +4882,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4929,13 +4915,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507047</v>
+        <v>507278</v>
       </c>
       <c r="R34" t="n">
-        <v>7053451</v>
+        <v>7053515</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4993,12 +4979,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5016,10 +5002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123591099</v>
+        <v>123577798</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5032,34 +5018,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506907</v>
+        <v>506927</v>
       </c>
       <c r="R35" t="n">
-        <v>7053220</v>
+        <v>7053299</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -5110,22 +5101,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5143,10 +5134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123583252</v>
+        <v>123579440</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>96957</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5155,31 +5146,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5188,13 +5179,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507086</v>
+        <v>507010</v>
       </c>
       <c r="R36" t="n">
-        <v>7053520</v>
+        <v>7053401</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5234,31 +5225,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5275,10 +5241,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123585825</v>
+        <v>123583498</v>
       </c>
       <c r="B37" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5291,39 +5257,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507140</v>
+        <v>507170</v>
       </c>
       <c r="R37" t="n">
-        <v>7053422</v>
+        <v>7053530</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5384,12 +5345,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5410,7 +5371,7 @@
         <v>123579557</v>
       </c>
       <c r="B38" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5514,7 +5475,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123581420</v>
+        <v>123583184</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -5554,10 +5515,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507128</v>
+        <v>507077</v>
       </c>
       <c r="R39" t="n">
-        <v>7053537</v>
+        <v>7053510</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -5641,10 +5602,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123582759</v>
+        <v>123587292</v>
       </c>
       <c r="B40" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5657,48 +5618,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507054</v>
+        <v>507134</v>
       </c>
       <c r="R40" t="n">
-        <v>7053507</v>
+        <v>7053449</v>
       </c>
       <c r="S40" t="n">
         <v>8</v>
@@ -5759,12 +5706,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5782,7 +5729,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123576556</v>
+        <v>123585702</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5822,13 +5769,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506963</v>
+        <v>507157</v>
       </c>
       <c r="R41" t="n">
-        <v>7053384</v>
+        <v>7053405</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5858,6 +5805,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5909,10 +5861,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123580927</v>
+        <v>123576777</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5925,21 +5877,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5949,13 +5901,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507115</v>
+        <v>506942</v>
       </c>
       <c r="R42" t="n">
-        <v>7053483</v>
+        <v>7053366</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5987,6 +5939,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6003,22 +5960,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6036,10 +5993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123582871</v>
+        <v>123577590</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6052,37 +6009,47 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507066</v>
+        <v>506932</v>
       </c>
       <c r="R43" t="n">
-        <v>7053479</v>
+        <v>7053304</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6114,6 +6081,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6140,12 +6112,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6163,7 +6135,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123583373</v>
+        <v>123585102</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -6197,24 +6169,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507115</v>
+        <v>507242</v>
       </c>
       <c r="R44" t="n">
-        <v>7053507</v>
+        <v>7053471</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6272,12 +6239,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6295,10 +6262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123577798</v>
+        <v>123576626</v>
       </c>
       <c r="B45" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6311,27 +6278,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6340,10 +6307,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506927</v>
+        <v>506978</v>
       </c>
       <c r="R45" t="n">
-        <v>7053299</v>
+        <v>7053390</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6394,22 +6361,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6427,10 +6394,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123576823</v>
+        <v>123583817</v>
       </c>
       <c r="B46" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6439,25 +6406,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6472,13 +6439,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506940</v>
+        <v>507164</v>
       </c>
       <c r="R46" t="n">
-        <v>7053366</v>
+        <v>7053542</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6510,11 +6477,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6531,22 +6493,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6564,10 +6526,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123589530</v>
+        <v>123583252</v>
       </c>
       <c r="B47" t="n">
-        <v>97369</v>
+        <v>79869</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6576,31 +6538,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6609,13 +6571,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507044</v>
+        <v>507086</v>
       </c>
       <c r="R47" t="n">
-        <v>7053131</v>
+        <v>7053520</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6659,6 +6621,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6676,10 +6658,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123579984</v>
+        <v>123584458</v>
       </c>
       <c r="B48" t="n">
-        <v>90986</v>
+        <v>91678</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6688,25 +6670,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6721,13 +6703,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507018</v>
+        <v>507220</v>
       </c>
       <c r="R48" t="n">
-        <v>7053429</v>
+        <v>7053559</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6759,6 +6741,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6785,12 +6772,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6808,7 +6795,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123585702</v>
+        <v>123576556</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -6848,13 +6835,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507157</v>
+        <v>506963</v>
       </c>
       <c r="R49" t="n">
-        <v>7053405</v>
+        <v>7053384</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6884,11 +6871,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6940,10 +6922,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123579440</v>
+        <v>123585185</v>
       </c>
       <c r="B50" t="n">
-        <v>97369</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6952,31 +6934,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6985,13 +6967,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507010</v>
+        <v>507197</v>
       </c>
       <c r="R50" t="n">
-        <v>7053401</v>
+        <v>7053490</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7031,6 +7013,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7047,7 +7054,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123584853</v>
+        <v>123586717</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -7087,13 +7094,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507238</v>
+        <v>507076</v>
       </c>
       <c r="R51" t="n">
-        <v>7053518</v>
+        <v>7053414</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7151,12 +7158,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7174,10 +7181,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123583498</v>
+        <v>123591258</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>100257</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7186,41 +7193,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507170</v>
+        <v>506882</v>
       </c>
       <c r="R52" t="n">
-        <v>7053530</v>
+        <v>7053247</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7264,26 +7276,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7301,10 +7293,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123588146</v>
+        <v>123580416</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7317,37 +7309,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507059</v>
+        <v>507047</v>
       </c>
       <c r="R53" t="n">
-        <v>7053347</v>
+        <v>7053451</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7405,12 +7402,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7428,7 +7425,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123576626</v>
+        <v>123577978</v>
       </c>
       <c r="B54" t="n">
         <v>91008</v>
@@ -7473,13 +7470,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506978</v>
+        <v>506936</v>
       </c>
       <c r="R54" t="n">
-        <v>7053390</v>
+        <v>7053351</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7560,10 +7557,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123580202</v>
+        <v>123580927</v>
       </c>
       <c r="B55" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7572,46 +7569,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507014</v>
+        <v>507115</v>
       </c>
       <c r="R55" t="n">
-        <v>7053440</v>
+        <v>7053483</v>
       </c>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7659,22 +7651,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7692,7 +7684,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123589076</v>
+        <v>123584853</v>
       </c>
       <c r="B56" t="n">
         <v>78788</v>
@@ -7732,13 +7724,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507050</v>
+        <v>507238</v>
       </c>
       <c r="R56" t="n">
-        <v>7053220</v>
+        <v>7053518</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7819,10 +7811,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123583817</v>
+        <v>123579984</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7835,27 +7827,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7864,10 +7856,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507164</v>
+        <v>507018</v>
       </c>
       <c r="R57" t="n">
-        <v>7053542</v>
+        <v>7053429</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7928,12 +7920,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7951,10 +7943,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123577978</v>
+        <v>123576823</v>
       </c>
       <c r="B58" t="n">
-        <v>91008</v>
+        <v>79898</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7963,31 +7955,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7996,13 +7988,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506936</v>
+        <v>506940</v>
       </c>
       <c r="R58" t="n">
-        <v>7053351</v>
+        <v>7053366</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8034,6 +8026,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8050,22 +8047,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8083,10 +8080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123591258</v>
+        <v>123589530</v>
       </c>
       <c r="B59" t="n">
-        <v>100682</v>
+        <v>96957</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8099,21 +8096,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8128,13 +8125,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506882</v>
+        <v>507044</v>
       </c>
       <c r="R59" t="n">
-        <v>7053247</v>
+        <v>7053131</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8195,7 +8192,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123585185</v>
+        <v>123591099</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -8229,21 +8226,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507197</v>
+        <v>506907</v>
       </c>
       <c r="R60" t="n">
-        <v>7053490</v>
+        <v>7053220</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -8327,10 +8319,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123583184</v>
+        <v>123582759</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8343,37 +8335,51 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507077</v>
+        <v>507054</v>
       </c>
       <c r="R61" t="n">
-        <v>7053510</v>
+        <v>7053507</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8431,12 +8437,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8454,10 +8460,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123586447</v>
+        <v>123581420</v>
       </c>
       <c r="B62" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8470,51 +8476,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507120</v>
+        <v>507128</v>
       </c>
       <c r="R62" t="n">
-        <v>7053421</v>
+        <v>7053537</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8546,11 +8538,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8563,6 +8550,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8580,10 +8587,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123584458</v>
+        <v>123580202</v>
       </c>
       <c r="B63" t="n">
-        <v>91678</v>
+        <v>79905</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8596,27 +8603,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8625,13 +8632,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507220</v>
+        <v>507014</v>
       </c>
       <c r="R63" t="n">
-        <v>7053559</v>
+        <v>7053440</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8663,11 +8670,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8684,22 +8686,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8717,10 +8719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123585014</v>
+        <v>123588146</v>
       </c>
       <c r="B64" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8729,46 +8731,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507278</v>
+        <v>507059</v>
       </c>
       <c r="R64" t="n">
-        <v>7053515</v>
+        <v>7053347</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8826,12 +8823,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8849,10 +8846,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123585102</v>
+        <v>123587645</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8861,38 +8858,57 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507242</v>
+        <v>507096</v>
       </c>
       <c r="R65" t="n">
-        <v>7053471</v>
+        <v>7053337</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8927,6 +8943,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8939,26 +8960,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8976,10 +8977,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123586717</v>
+        <v>123586447</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8992,37 +8993,51 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507076</v>
+        <v>507120</v>
       </c>
       <c r="R66" t="n">
-        <v>7053414</v>
+        <v>7053421</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9054,6 +9069,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9066,26 +9086,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123590101</v>
+        <v>123582066</v>
       </c>
       <c r="B67" t="n">
         <v>57491</v>
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507030</v>
+        <v>507073</v>
       </c>
       <c r="R67" t="n">
-        <v>7053146</v>
+        <v>7053530</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9245,7 +9245,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123588546</v>
+        <v>123579421</v>
       </c>
       <c r="B68" t="n">
         <v>57491</v>
@@ -9281,7 +9281,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9295,13 +9295,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507024</v>
+        <v>507014</v>
       </c>
       <c r="R68" t="n">
-        <v>7053316</v>
+        <v>7053420</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9387,7 +9387,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123579421</v>
+        <v>123588546</v>
       </c>
       <c r="B69" t="n">
         <v>57491</v>
@@ -9423,7 +9423,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507014</v>
+        <v>507024</v>
       </c>
       <c r="R69" t="n">
-        <v>7053420</v>
+        <v>7053316</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9671,10 +9671,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123590902</v>
+        <v>123772770</v>
       </c>
       <c r="B71" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9687,47 +9687,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506945</v>
+        <v>507241</v>
       </c>
       <c r="R71" t="n">
-        <v>7053117</v>
+        <v>7053498</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9751,17 +9744,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9770,6 +9763,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9790,12 +9784,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9813,10 +9807,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123772770</v>
+        <v>123590902</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9829,40 +9823,47 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507241</v>
+        <v>506945</v>
       </c>
       <c r="R72" t="n">
-        <v>7053498</v>
+        <v>7053117</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9886,17 +9887,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9905,7 +9906,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123772501</v>
+        <v>123590101</v>
       </c>
       <c r="B73" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9965,44 +9965,47 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507174</v>
+        <v>507030</v>
       </c>
       <c r="R73" t="n">
-        <v>7053322</v>
+        <v>7053146</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10026,12 +10029,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10040,7 +10048,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10049,11 +10056,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ73" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10066,12 +10068,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10089,10 +10091,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123581252</v>
+        <v>123772501</v>
       </c>
       <c r="B74" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10105,42 +10107,44 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507113</v>
+        <v>507174</v>
       </c>
       <c r="R74" t="n">
-        <v>7053527</v>
+        <v>7053322</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10164,17 +10168,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10183,6 +10182,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10191,24 +10191,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10226,10 +10231,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123582066</v>
+        <v>123581252</v>
       </c>
       <c r="B75" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10242,32 +10247,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507073</v>
+        <v>507113</v>
       </c>
       <c r="R75" t="n">
-        <v>7053530</v>
+        <v>7053527</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -6135,10 +6135,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123585102</v>
+        <v>123576626</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6151,37 +6151,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507242</v>
+        <v>506978</v>
       </c>
       <c r="R44" t="n">
-        <v>7053471</v>
+        <v>7053390</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6239,12 +6244,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6262,10 +6267,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123576626</v>
+        <v>123585102</v>
       </c>
       <c r="B45" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6278,42 +6283,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506978</v>
+        <v>507242</v>
       </c>
       <c r="R45" t="n">
-        <v>7053390</v>
+        <v>7053471</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6394,10 +6394,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123583817</v>
+        <v>123583252</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6410,27 +6410,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507164</v>
+        <v>507086</v>
       </c>
       <c r="R46" t="n">
-        <v>7053542</v>
+        <v>7053520</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -6493,22 +6493,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6526,10 +6526,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123583252</v>
+        <v>123584458</v>
       </c>
       <c r="B47" t="n">
-        <v>79869</v>
+        <v>91678</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6538,31 +6538,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507086</v>
+        <v>507220</v>
       </c>
       <c r="R47" t="n">
-        <v>7053520</v>
+        <v>7053559</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6609,6 +6609,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6625,22 +6630,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6658,10 +6663,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123584458</v>
+        <v>123583817</v>
       </c>
       <c r="B48" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6670,31 +6675,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6703,13 +6708,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507220</v>
+        <v>507164</v>
       </c>
       <c r="R48" t="n">
-        <v>7053559</v>
+        <v>7053542</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6741,11 +6746,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6772,12 +6772,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123588146</v>
+        <v>123586447</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8735,37 +8735,51 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507059</v>
+        <v>507120</v>
       </c>
       <c r="R64" t="n">
-        <v>7053347</v>
+        <v>7053421</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8797,6 +8811,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8809,26 +8828,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8846,10 +8845,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123587645</v>
+        <v>123588146</v>
       </c>
       <c r="B65" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8858,60 +8857,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507096</v>
+        <v>507059</v>
       </c>
       <c r="R65" t="n">
-        <v>7053337</v>
+        <v>7053347</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8943,11 +8923,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8960,6 +8935,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8977,10 +8972,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123586447</v>
+        <v>123587645</v>
       </c>
       <c r="B66" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8989,35 +8984,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9027,17 +9027,17 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507120</v>
+        <v>507096</v>
       </c>
       <c r="R66" t="n">
-        <v>7053421</v>
+        <v>7053337</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123588776</v>
+        <v>123579984</v>
       </c>
       <c r="B27" t="n">
-        <v>79870</v>
+        <v>90986</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3972,27 +3972,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507044</v>
+        <v>507018</v>
       </c>
       <c r="R27" t="n">
-        <v>7053321</v>
+        <v>7053429</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -4039,11 +4039,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4060,22 +4055,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4093,7 +4088,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123589076</v>
+        <v>123577656</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -4133,13 +4128,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507050</v>
+        <v>506944</v>
       </c>
       <c r="R28" t="n">
-        <v>7053220</v>
+        <v>7053309</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4220,10 +4215,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123577656</v>
+        <v>123591258</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>100257</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4232,41 +4227,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506944</v>
+        <v>506882</v>
       </c>
       <c r="R29" t="n">
-        <v>7053309</v>
+        <v>7053247</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4310,26 +4310,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4347,7 +4327,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123583373</v>
+        <v>123588146</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -4381,24 +4361,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507115</v>
+        <v>507059</v>
       </c>
       <c r="R30" t="n">
-        <v>7053507</v>
+        <v>7053347</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4456,12 +4431,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4479,10 +4454,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123585825</v>
+        <v>123581420</v>
       </c>
       <c r="B31" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4495,39 +4470,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507140</v>
+        <v>507128</v>
       </c>
       <c r="R31" t="n">
-        <v>7053422</v>
+        <v>7053537</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -4588,12 +4558,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4611,7 +4581,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123582871</v>
+        <v>123585185</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -4645,19 +4615,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507066</v>
+        <v>507197</v>
       </c>
       <c r="R32" t="n">
-        <v>7053479</v>
+        <v>7053490</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4738,10 +4713,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123585385</v>
+        <v>123583252</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4754,27 +4729,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4783,13 +4758,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507169</v>
+        <v>507086</v>
       </c>
       <c r="R33" t="n">
-        <v>7053461</v>
+        <v>7053520</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4837,22 +4812,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4870,10 +4845,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123585014</v>
+        <v>123577978</v>
       </c>
       <c r="B34" t="n">
-        <v>91678</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4882,25 +4857,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4915,13 +4890,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507278</v>
+        <v>506936</v>
       </c>
       <c r="R34" t="n">
-        <v>7053515</v>
+        <v>7053351</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5002,10 +4977,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123577798</v>
+        <v>123580416</v>
       </c>
       <c r="B35" t="n">
-        <v>79869</v>
+        <v>90986</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5018,27 +4993,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5047,13 +5022,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506927</v>
+        <v>507047</v>
       </c>
       <c r="R35" t="n">
-        <v>7053299</v>
+        <v>7053451</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5101,22 +5076,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5134,10 +5109,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123579440</v>
+        <v>123584458</v>
       </c>
       <c r="B36" t="n">
-        <v>96957</v>
+        <v>91678</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5150,27 +5125,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5179,13 +5154,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507010</v>
+        <v>507220</v>
       </c>
       <c r="R36" t="n">
-        <v>7053401</v>
+        <v>7053559</v>
       </c>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5217,6 +5192,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5225,6 +5205,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5241,10 +5246,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123583498</v>
+        <v>123588776</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5257,34 +5262,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507170</v>
+        <v>507044</v>
       </c>
       <c r="R37" t="n">
-        <v>7053530</v>
+        <v>7053321</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5319,6 +5329,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5335,22 +5350,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5368,10 +5383,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123579557</v>
+        <v>123583817</v>
       </c>
       <c r="B38" t="n">
-        <v>100257</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5380,31 +5395,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5413,10 +5428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507035</v>
+        <v>507164</v>
       </c>
       <c r="R38" t="n">
-        <v>7053385</v>
+        <v>7053542</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5459,6 +5474,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5475,10 +5515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123583184</v>
+        <v>123585014</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5487,41 +5527,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507077</v>
+        <v>507278</v>
       </c>
       <c r="R39" t="n">
-        <v>7053510</v>
+        <v>7053515</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5579,12 +5624,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5602,7 +5647,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123587292</v>
+        <v>123583184</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -5642,13 +5687,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507134</v>
+        <v>507077</v>
       </c>
       <c r="R40" t="n">
-        <v>7053449</v>
+        <v>7053510</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5729,10 +5774,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123585702</v>
+        <v>123577798</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5745,34 +5790,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507157</v>
+        <v>506927</v>
       </c>
       <c r="R41" t="n">
-        <v>7053405</v>
+        <v>7053299</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5807,11 +5857,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5828,22 +5873,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5861,10 +5906,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123576777</v>
+        <v>123586717</v>
       </c>
       <c r="B42" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5877,21 +5922,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5901,13 +5946,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506942</v>
+        <v>507076</v>
       </c>
       <c r="R42" t="n">
-        <v>7053366</v>
+        <v>7053414</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5939,11 +5984,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5960,22 +6000,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6135,10 +6175,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123576626</v>
+        <v>123580927</v>
       </c>
       <c r="B44" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6151,42 +6191,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506978</v>
+        <v>507115</v>
       </c>
       <c r="R44" t="n">
-        <v>7053390</v>
+        <v>7053483</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6244,12 +6279,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6267,7 +6302,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123585102</v>
+        <v>123584853</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -6307,13 +6342,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507242</v>
+        <v>507238</v>
       </c>
       <c r="R45" t="n">
-        <v>7053471</v>
+        <v>7053518</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6394,10 +6429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123583252</v>
+        <v>123587292</v>
       </c>
       <c r="B46" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6410,42 +6445,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507086</v>
+        <v>507134</v>
       </c>
       <c r="R46" t="n">
-        <v>7053520</v>
+        <v>7053449</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6493,22 +6523,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6526,10 +6556,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123584458</v>
+        <v>123585702</v>
       </c>
       <c r="B47" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6538,46 +6568,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507220</v>
+        <v>507157</v>
       </c>
       <c r="R47" t="n">
-        <v>7053559</v>
+        <v>7053405</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6611,7 +6636,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6640,12 +6665,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6663,7 +6688,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123583817</v>
+        <v>123576556</v>
       </c>
       <c r="B48" t="n">
         <v>78788</v>
@@ -6697,24 +6722,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507164</v>
+        <v>506963</v>
       </c>
       <c r="R48" t="n">
-        <v>7053542</v>
+        <v>7053384</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6795,7 +6815,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123576556</v>
+        <v>123582871</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -6835,13 +6855,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506963</v>
+        <v>507066</v>
       </c>
       <c r="R49" t="n">
-        <v>7053384</v>
+        <v>7053479</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6922,10 +6942,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123585185</v>
+        <v>123579557</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>100257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6934,31 +6954,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6967,10 +6987,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507197</v>
+        <v>507035</v>
       </c>
       <c r="R50" t="n">
-        <v>7053490</v>
+        <v>7053385</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -7013,31 +7033,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7054,10 +7049,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123586717</v>
+        <v>123576823</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7066,41 +7061,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507076</v>
+        <v>506940</v>
       </c>
       <c r="R51" t="n">
-        <v>7053414</v>
+        <v>7053366</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7132,6 +7132,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7148,22 +7153,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7181,10 +7186,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123591258</v>
+        <v>123583498</v>
       </c>
       <c r="B52" t="n">
-        <v>100257</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7193,46 +7198,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506882</v>
+        <v>507170</v>
       </c>
       <c r="R52" t="n">
-        <v>7053247</v>
+        <v>7053530</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7276,6 +7276,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7293,10 +7313,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123580416</v>
+        <v>123585102</v>
       </c>
       <c r="B53" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7309,42 +7329,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507047</v>
+        <v>507242</v>
       </c>
       <c r="R53" t="n">
-        <v>7053451</v>
+        <v>7053471</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7402,12 +7417,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7425,10 +7440,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123577978</v>
+        <v>123591099</v>
       </c>
       <c r="B54" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7441,42 +7456,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506936</v>
+        <v>506907</v>
       </c>
       <c r="R54" t="n">
-        <v>7053351</v>
+        <v>7053220</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7534,12 +7544,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7557,10 +7567,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123580927</v>
+        <v>123587645</v>
       </c>
       <c r="B55" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7569,41 +7579,60 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507115</v>
+        <v>507096</v>
       </c>
       <c r="R55" t="n">
-        <v>7053483</v>
+        <v>7053337</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7635,6 +7664,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7647,26 +7681,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7684,10 +7698,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123584853</v>
+        <v>123589530</v>
       </c>
       <c r="B56" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7696,41 +7710,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507238</v>
+        <v>507044</v>
       </c>
       <c r="R56" t="n">
-        <v>7053518</v>
+        <v>7053131</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7774,26 +7793,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7811,10 +7810,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123579984</v>
+        <v>123585825</v>
       </c>
       <c r="B57" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7827,21 +7826,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7856,10 +7855,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507018</v>
+        <v>507140</v>
       </c>
       <c r="R57" t="n">
-        <v>7053429</v>
+        <v>7053422</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7943,10 +7942,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123576823</v>
+        <v>123585385</v>
       </c>
       <c r="B58" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7955,25 +7954,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7988,10 +7987,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506940</v>
+        <v>507169</v>
       </c>
       <c r="R58" t="n">
-        <v>7053366</v>
+        <v>7053461</v>
       </c>
       <c r="S58" t="n">
         <v>8</v>
@@ -8026,11 +8025,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -8047,22 +8041,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8080,10 +8074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123589530</v>
+        <v>123576777</v>
       </c>
       <c r="B59" t="n">
-        <v>96957</v>
+        <v>79869</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8092,46 +8086,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507044</v>
+        <v>506942</v>
       </c>
       <c r="R59" t="n">
-        <v>7053131</v>
+        <v>7053366</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8163,6 +8152,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8175,6 +8169,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8192,7 +8206,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123591099</v>
+        <v>123583373</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -8226,19 +8240,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506907</v>
+        <v>507115</v>
       </c>
       <c r="R60" t="n">
-        <v>7053220</v>
+        <v>7053507</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8296,12 +8315,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8319,10 +8338,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123582759</v>
+        <v>123589076</v>
       </c>
       <c r="B61" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8335,51 +8354,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507054</v>
+        <v>507050</v>
       </c>
       <c r="R61" t="n">
-        <v>7053507</v>
+        <v>7053220</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8437,12 +8442,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8460,10 +8465,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123581420</v>
+        <v>123586447</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8476,37 +8481,51 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507128</v>
+        <v>507120</v>
       </c>
       <c r="R62" t="n">
-        <v>7053537</v>
+        <v>7053421</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8538,6 +8557,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8550,26 +8574,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8719,10 +8723,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123586447</v>
+        <v>123582759</v>
       </c>
       <c r="B64" t="n">
-        <v>57644</v>
+        <v>91008</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8735,51 +8739,51 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507120</v>
+        <v>507054</v>
       </c>
       <c r="R64" t="n">
-        <v>7053421</v>
+        <v>7053507</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8811,11 +8815,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8828,6 +8827,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8845,10 +8864,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123588146</v>
+        <v>123579440</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8857,41 +8876,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507059</v>
+        <v>507010</v>
       </c>
       <c r="R65" t="n">
-        <v>7053347</v>
+        <v>7053401</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8931,31 +8955,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8972,10 +8971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123587645</v>
+        <v>123576626</v>
       </c>
       <c r="B66" t="n">
-        <v>57861</v>
+        <v>91008</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8984,45 +8983,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9031,13 +9016,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507096</v>
+        <v>506978</v>
       </c>
       <c r="R66" t="n">
-        <v>7053337</v>
+        <v>7053390</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9069,11 +9054,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -9086,6 +9066,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123582066</v>
+        <v>123772501</v>
       </c>
       <c r="B67" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9119,47 +9119,44 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507073</v>
+        <v>507174</v>
       </c>
       <c r="R67" t="n">
-        <v>7053530</v>
+        <v>7053322</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9183,17 +9180,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9202,6 +9194,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9210,6 +9203,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ67" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9222,12 +9220,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9245,10 +9243,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123579421</v>
+        <v>123772770</v>
       </c>
       <c r="B68" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9261,47 +9259,40 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507014</v>
+        <v>507241</v>
       </c>
       <c r="R68" t="n">
-        <v>7053420</v>
+        <v>7053498</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9325,17 +9316,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9344,6 +9335,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9364,12 +9356,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9387,10 +9379,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123588546</v>
+        <v>123581252</v>
       </c>
       <c r="B69" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9403,32 +9395,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9437,13 +9424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507024</v>
+        <v>507113</v>
       </c>
       <c r="R69" t="n">
-        <v>7053316</v>
+        <v>7053527</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9477,7 +9464,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9496,22 +9483,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9529,7 +9516,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123580751</v>
+        <v>123582066</v>
       </c>
       <c r="B70" t="n">
         <v>57491</v>
@@ -9565,7 +9552,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9579,13 +9566,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507106</v>
+        <v>507073</v>
       </c>
       <c r="R70" t="n">
-        <v>7053481</v>
+        <v>7053530</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9619,7 +9606,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9671,10 +9658,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123772770</v>
+        <v>123590101</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9687,40 +9674,47 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507241</v>
+        <v>507030</v>
       </c>
       <c r="R71" t="n">
-        <v>7053498</v>
+        <v>7053146</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9744,17 +9738,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9763,7 +9757,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9784,12 +9777,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9807,7 +9800,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123590902</v>
+        <v>123588546</v>
       </c>
       <c r="B72" t="n">
         <v>57491</v>
@@ -9843,7 +9836,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -9857,13 +9850,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506945</v>
+        <v>507024</v>
       </c>
       <c r="R72" t="n">
-        <v>7053117</v>
+        <v>7053316</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9897,7 +9890,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9949,7 +9942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123590101</v>
+        <v>123580751</v>
       </c>
       <c r="B73" t="n">
         <v>57491</v>
@@ -9985,7 +9978,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9999,13 +9992,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507030</v>
+        <v>507106</v>
       </c>
       <c r="R73" t="n">
-        <v>7053146</v>
+        <v>7053481</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10039,7 +10032,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10091,10 +10084,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123772501</v>
+        <v>123579421</v>
       </c>
       <c r="B74" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10107,44 +10100,47 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507174</v>
+        <v>507014</v>
       </c>
       <c r="R74" t="n">
-        <v>7053322</v>
+        <v>7053420</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10168,12 +10164,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10182,7 +10183,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10191,11 +10191,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ74" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10208,12 +10203,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10231,10 +10226,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123581252</v>
+        <v>123590902</v>
       </c>
       <c r="B75" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10247,27 +10242,32 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507113</v>
+        <v>506945</v>
       </c>
       <c r="R75" t="n">
-        <v>7053527</v>
+        <v>7053117</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123579984</v>
+        <v>123584458</v>
       </c>
       <c r="B27" t="n">
-        <v>90986</v>
+        <v>91678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3968,25 +3968,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507018</v>
+        <v>507220</v>
       </c>
       <c r="R27" t="n">
-        <v>7053429</v>
+        <v>7053559</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4039,6 +4039,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4065,12 +4070,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4088,10 +4093,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123577656</v>
+        <v>123580416</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4104,37 +4109,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506944</v>
+        <v>507047</v>
       </c>
       <c r="R28" t="n">
-        <v>7053309</v>
+        <v>7053451</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4192,12 +4202,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4215,10 +4225,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123591258</v>
+        <v>123579440</v>
       </c>
       <c r="B29" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4231,21 +4241,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4260,13 +4270,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506882</v>
+        <v>507010</v>
       </c>
       <c r="R29" t="n">
-        <v>7053247</v>
+        <v>7053401</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4306,11 +4316,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4327,10 +4332,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123588146</v>
+        <v>123576626</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4343,34 +4348,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507059</v>
+        <v>506978</v>
       </c>
       <c r="R30" t="n">
-        <v>7053347</v>
+        <v>7053390</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4431,12 +4441,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4454,7 +4464,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123581420</v>
+        <v>123583373</v>
       </c>
       <c r="B31" t="n">
         <v>78788</v>
@@ -4488,19 +4498,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507128</v>
+        <v>507115</v>
       </c>
       <c r="R31" t="n">
-        <v>7053537</v>
+        <v>7053507</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4558,12 +4573,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4581,7 +4596,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123585185</v>
+        <v>123577656</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -4615,21 +4630,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507197</v>
+        <v>506944</v>
       </c>
       <c r="R32" t="n">
-        <v>7053490</v>
+        <v>7053309</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4713,7 +4723,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123583252</v>
+        <v>123577798</v>
       </c>
       <c r="B33" t="n">
         <v>79869</v>
@@ -4758,10 +4768,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507086</v>
+        <v>506927</v>
       </c>
       <c r="R33" t="n">
-        <v>7053520</v>
+        <v>7053299</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -4845,10 +4855,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123577978</v>
+        <v>123580202</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>79905</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4857,31 +4867,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4890,13 +4900,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506936</v>
+        <v>507014</v>
       </c>
       <c r="R34" t="n">
-        <v>7053351</v>
+        <v>7053440</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4944,22 +4954,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4977,10 +4987,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123580416</v>
+        <v>123585825</v>
       </c>
       <c r="B35" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4993,21 +5003,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5022,13 +5032,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507047</v>
+        <v>507140</v>
       </c>
       <c r="R35" t="n">
-        <v>7053451</v>
+        <v>7053422</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5086,12 +5096,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5109,10 +5119,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123584458</v>
+        <v>123591099</v>
       </c>
       <c r="B36" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5121,46 +5131,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507220</v>
+        <v>506907</v>
       </c>
       <c r="R36" t="n">
-        <v>7053559</v>
+        <v>7053220</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5192,11 +5197,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5223,12 +5223,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123583817</v>
+        <v>123580927</v>
       </c>
       <c r="B38" t="n">
         <v>78788</v>
@@ -5417,24 +5417,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507164</v>
+        <v>507115</v>
       </c>
       <c r="R38" t="n">
-        <v>7053542</v>
+        <v>7053483</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5515,10 +5510,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123585014</v>
+        <v>123584853</v>
       </c>
       <c r="B39" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5527,43 +5522,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507278</v>
+        <v>507238</v>
       </c>
       <c r="R39" t="n">
-        <v>7053515</v>
+        <v>7053518</v>
       </c>
       <c r="S39" t="n">
         <v>7</v>
@@ -5624,12 +5614,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5774,10 +5764,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123577798</v>
+        <v>123585385</v>
       </c>
       <c r="B41" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5790,27 +5780,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5819,13 +5809,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506927</v>
+        <v>507169</v>
       </c>
       <c r="R41" t="n">
-        <v>7053299</v>
+        <v>7053461</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5873,22 +5863,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5906,10 +5896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123586717</v>
+        <v>123576823</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5918,41 +5908,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507076</v>
+        <v>506940</v>
       </c>
       <c r="R42" t="n">
-        <v>7053414</v>
+        <v>7053366</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5984,6 +5979,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6000,22 +6000,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6033,10 +6033,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123577590</v>
+        <v>123591258</v>
       </c>
       <c r="B43" t="n">
-        <v>57491</v>
+        <v>100257</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6045,36 +6045,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6083,13 +6078,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506932</v>
+        <v>506882</v>
       </c>
       <c r="R43" t="n">
-        <v>7053304</v>
+        <v>7053247</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6121,11 +6116,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6138,26 +6128,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6175,10 +6145,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123580927</v>
+        <v>123579984</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6191,37 +6161,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507115</v>
+        <v>507018</v>
       </c>
       <c r="R44" t="n">
-        <v>7053483</v>
+        <v>7053429</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6279,12 +6254,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6302,10 +6277,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123584853</v>
+        <v>123585014</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6314,38 +6289,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507238</v>
+        <v>507278</v>
       </c>
       <c r="R45" t="n">
-        <v>7053518</v>
+        <v>7053515</v>
       </c>
       <c r="S45" t="n">
         <v>7</v>
@@ -6406,12 +6386,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6429,10 +6409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123587292</v>
+        <v>123587645</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6441,41 +6421,60 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507134</v>
+        <v>507096</v>
       </c>
       <c r="R46" t="n">
-        <v>7053449</v>
+        <v>7053337</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6507,6 +6506,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6519,26 +6523,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6556,7 +6540,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123585702</v>
+        <v>123585185</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -6590,16 +6574,21 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507157</v>
+        <v>507197</v>
       </c>
       <c r="R47" t="n">
-        <v>7053405</v>
+        <v>7053490</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -6632,11 +6621,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6688,10 +6672,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123576556</v>
+        <v>123589530</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6700,41 +6684,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506963</v>
+        <v>507044</v>
       </c>
       <c r="R48" t="n">
-        <v>7053384</v>
+        <v>7053131</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6778,26 +6767,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6815,10 +6784,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123582871</v>
+        <v>123579557</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>100257</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6827,41 +6796,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507066</v>
+        <v>507035</v>
       </c>
       <c r="R49" t="n">
-        <v>7053479</v>
+        <v>7053385</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6901,31 +6875,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6942,10 +6891,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123579557</v>
+        <v>123583817</v>
       </c>
       <c r="B50" t="n">
-        <v>100257</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6954,31 +6903,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6987,10 +6936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507035</v>
+        <v>507164</v>
       </c>
       <c r="R50" t="n">
-        <v>7053385</v>
+        <v>7053542</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -7033,6 +6982,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7049,10 +7023,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123576823</v>
+        <v>123583252</v>
       </c>
       <c r="B51" t="n">
-        <v>79898</v>
+        <v>79869</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7061,31 +7035,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7094,13 +7068,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506940</v>
+        <v>507086</v>
       </c>
       <c r="R51" t="n">
-        <v>7053366</v>
+        <v>7053520</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7130,11 +7104,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7186,7 +7155,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123583498</v>
+        <v>123581420</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -7226,10 +7195,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507170</v>
+        <v>507128</v>
       </c>
       <c r="R52" t="n">
-        <v>7053530</v>
+        <v>7053537</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -7290,12 +7259,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7313,10 +7282,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123585102</v>
+        <v>123576777</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7329,21 +7298,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7353,13 +7322,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507242</v>
+        <v>506942</v>
       </c>
       <c r="R53" t="n">
-        <v>7053471</v>
+        <v>7053366</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7391,6 +7360,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7407,22 +7381,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7440,7 +7414,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123591099</v>
+        <v>123582871</v>
       </c>
       <c r="B54" t="n">
         <v>78788</v>
@@ -7480,13 +7454,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506907</v>
+        <v>507066</v>
       </c>
       <c r="R54" t="n">
-        <v>7053220</v>
+        <v>7053479</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7567,10 +7541,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123587645</v>
+        <v>123586717</v>
       </c>
       <c r="B55" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7579,60 +7553,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507096</v>
+        <v>507076</v>
       </c>
       <c r="R55" t="n">
-        <v>7053337</v>
+        <v>7053414</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7664,11 +7619,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7681,6 +7631,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7698,10 +7668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123589530</v>
+        <v>123587292</v>
       </c>
       <c r="B56" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7710,46 +7680,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507044</v>
+        <v>507134</v>
       </c>
       <c r="R56" t="n">
-        <v>7053131</v>
+        <v>7053449</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7793,6 +7758,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7810,10 +7795,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123585825</v>
+        <v>123585702</v>
       </c>
       <c r="B57" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7826,39 +7811,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507140</v>
+        <v>507157</v>
       </c>
       <c r="R57" t="n">
-        <v>7053422</v>
+        <v>7053405</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7893,6 +7873,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7919,12 +7904,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7942,7 +7927,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123585385</v>
+        <v>123585102</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -7976,24 +7961,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507169</v>
+        <v>507242</v>
       </c>
       <c r="R58" t="n">
-        <v>7053461</v>
+        <v>7053471</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8074,10 +8054,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123576777</v>
+        <v>123589076</v>
       </c>
       <c r="B59" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8090,21 +8070,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8114,10 +8094,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506942</v>
+        <v>507050</v>
       </c>
       <c r="R59" t="n">
-        <v>7053366</v>
+        <v>7053220</v>
       </c>
       <c r="S59" t="n">
         <v>11</v>
@@ -8152,11 +8132,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8173,22 +8148,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8206,10 +8181,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123583373</v>
+        <v>123577978</v>
       </c>
       <c r="B60" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8222,27 +8197,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8251,13 +8226,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507115</v>
+        <v>506936</v>
       </c>
       <c r="R60" t="n">
-        <v>7053507</v>
+        <v>7053351</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8338,10 +8313,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123589076</v>
+        <v>123582759</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8354,37 +8329,51 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507050</v>
+        <v>507054</v>
       </c>
       <c r="R61" t="n">
-        <v>7053220</v>
+        <v>7053507</v>
       </c>
       <c r="S61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8442,12 +8431,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8465,10 +8454,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123586447</v>
+        <v>123577590</v>
       </c>
       <c r="B62" t="n">
-        <v>57644</v>
+        <v>57491</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8481,31 +8470,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8515,14 +8500,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507120</v>
+        <v>506932</v>
       </c>
       <c r="R62" t="n">
-        <v>7053421</v>
+        <v>7053304</v>
       </c>
       <c r="S62" t="n">
         <v>7</v>
@@ -8559,7 +8544,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8574,6 +8559,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8591,10 +8596,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123580202</v>
+        <v>123576556</v>
       </c>
       <c r="B63" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8603,46 +8608,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507014</v>
+        <v>506963</v>
       </c>
       <c r="R63" t="n">
-        <v>7053440</v>
+        <v>7053384</v>
       </c>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8690,22 +8690,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123582759</v>
+        <v>123586447</v>
       </c>
       <c r="B64" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8739,51 +8739,51 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507054</v>
+        <v>507120</v>
       </c>
       <c r="R64" t="n">
-        <v>7053507</v>
+        <v>7053421</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8815,6 +8815,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8827,26 +8832,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8864,10 +8849,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123579440</v>
+        <v>123588146</v>
       </c>
       <c r="B65" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8876,46 +8861,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507010</v>
+        <v>507059</v>
       </c>
       <c r="R65" t="n">
-        <v>7053401</v>
+        <v>7053347</v>
       </c>
       <c r="S65" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8955,6 +8935,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8971,10 +8976,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123576626</v>
+        <v>123583498</v>
       </c>
       <c r="B66" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8987,39 +8992,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506978</v>
+        <v>507170</v>
       </c>
       <c r="R66" t="n">
-        <v>7053390</v>
+        <v>7053530</v>
       </c>
       <c r="S66" t="n">
         <v>9</v>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123772501</v>
+        <v>123581252</v>
       </c>
       <c r="B67" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9119,44 +9119,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507174</v>
+        <v>507113</v>
       </c>
       <c r="R67" t="n">
-        <v>7053322</v>
+        <v>7053527</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9180,12 +9178,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9194,7 +9197,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9203,29 +9205,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9243,10 +9240,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123772770</v>
+        <v>123772501</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9259,26 +9256,30 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9286,10 +9287,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507241</v>
+        <v>507174</v>
       </c>
       <c r="R68" t="n">
-        <v>7053498</v>
+        <v>7053322</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9324,11 +9325,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -9344,6 +9340,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ68" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9356,12 +9357,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9379,10 +9380,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123581252</v>
+        <v>123772770</v>
       </c>
       <c r="B69" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9395,42 +9396,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507113</v>
+        <v>507241</v>
       </c>
       <c r="R69" t="n">
-        <v>7053527</v>
+        <v>7053498</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9454,17 +9453,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9473,6 +9472,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9483,22 +9483,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123582066</v>
+        <v>123588546</v>
       </c>
       <c r="B70" t="n">
         <v>57491</v>
@@ -9552,7 +9552,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9566,13 +9566,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507073</v>
+        <v>507024</v>
       </c>
       <c r="R70" t="n">
-        <v>7053530</v>
+        <v>7053316</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9658,7 +9658,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123590101</v>
+        <v>123580751</v>
       </c>
       <c r="B71" t="n">
         <v>57491</v>
@@ -9694,7 +9694,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9708,13 +9708,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507030</v>
+        <v>507106</v>
       </c>
       <c r="R71" t="n">
-        <v>7053146</v>
+        <v>7053481</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9800,7 +9800,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123588546</v>
+        <v>123590101</v>
       </c>
       <c r="B72" t="n">
         <v>57491</v>
@@ -9836,7 +9836,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -9850,13 +9850,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507024</v>
+        <v>507030</v>
       </c>
       <c r="R72" t="n">
-        <v>7053316</v>
+        <v>7053146</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9942,7 +9942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123580751</v>
+        <v>123590902</v>
       </c>
       <c r="B73" t="n">
         <v>57491</v>
@@ -9978,7 +9978,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9992,13 +9992,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507106</v>
+        <v>506945</v>
       </c>
       <c r="R73" t="n">
-        <v>7053481</v>
+        <v>7053117</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10226,7 +10226,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123590902</v>
+        <v>123582066</v>
       </c>
       <c r="B75" t="n">
         <v>57491</v>
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506945</v>
+        <v>507073</v>
       </c>
       <c r="R75" t="n">
-        <v>7053117</v>
+        <v>7053530</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123584458</v>
+        <v>123588776</v>
       </c>
       <c r="B27" t="n">
-        <v>91678</v>
+        <v>79870</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3968,31 +3968,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507220</v>
+        <v>507044</v>
       </c>
       <c r="R27" t="n">
-        <v>7053559</v>
+        <v>7053321</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
+          <t>Enstaka bålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4060,22 +4060,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123580416</v>
+        <v>123583184</v>
       </c>
       <c r="B28" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4109,42 +4109,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507047</v>
+        <v>507077</v>
       </c>
       <c r="R28" t="n">
-        <v>7053451</v>
+        <v>7053510</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4202,12 +4197,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4225,10 +4220,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123579440</v>
+        <v>123591258</v>
       </c>
       <c r="B29" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4241,21 +4236,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4270,13 +4265,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507010</v>
+        <v>506882</v>
       </c>
       <c r="R29" t="n">
-        <v>7053401</v>
+        <v>7053247</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4316,6 +4311,11 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123576626</v>
+        <v>123581420</v>
       </c>
       <c r="B30" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4348,39 +4348,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506978</v>
+        <v>507128</v>
       </c>
       <c r="R30" t="n">
-        <v>7053390</v>
+        <v>7053537</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4441,12 +4436,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4464,7 +4459,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123583373</v>
+        <v>123582871</v>
       </c>
       <c r="B31" t="n">
         <v>78788</v>
@@ -4498,24 +4493,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507115</v>
+        <v>507066</v>
       </c>
       <c r="R31" t="n">
-        <v>7053507</v>
+        <v>7053479</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4573,12 +4563,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4596,7 +4586,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123577656</v>
+        <v>123580927</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -4636,13 +4626,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506944</v>
+        <v>507115</v>
       </c>
       <c r="R32" t="n">
-        <v>7053309</v>
+        <v>7053483</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4723,10 +4713,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123577798</v>
+        <v>123577590</v>
       </c>
       <c r="B33" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4739,27 +4729,32 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4768,13 +4763,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506927</v>
+        <v>506932</v>
       </c>
       <c r="R33" t="n">
-        <v>7053299</v>
+        <v>7053304</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4806,6 +4801,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4822,22 +4822,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123580202</v>
+        <v>123576777</v>
       </c>
       <c r="B34" t="n">
-        <v>79905</v>
+        <v>79869</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4867,46 +4867,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507014</v>
+        <v>506942</v>
       </c>
       <c r="R34" t="n">
-        <v>7053440</v>
+        <v>7053366</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4938,6 +4933,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123585825</v>
+        <v>123583252</v>
       </c>
       <c r="B35" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5003,27 +5003,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507140</v>
+        <v>507086</v>
       </c>
       <c r="R35" t="n">
-        <v>7053422</v>
+        <v>7053520</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
@@ -5086,22 +5086,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123591099</v>
+        <v>123576556</v>
       </c>
       <c r="B36" t="n">
         <v>78788</v>
@@ -5159,13 +5159,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506907</v>
+        <v>506963</v>
       </c>
       <c r="R36" t="n">
-        <v>7053220</v>
+        <v>7053384</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123588776</v>
+        <v>123588146</v>
       </c>
       <c r="B37" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5262,39 +5262,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507044</v>
+        <v>507059</v>
       </c>
       <c r="R37" t="n">
-        <v>7053321</v>
+        <v>7053347</v>
       </c>
       <c r="S37" t="n">
         <v>9</v>
@@ -5329,11 +5324,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5350,22 +5340,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5383,10 +5373,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123580927</v>
+        <v>123584458</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5395,38 +5385,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507115</v>
+        <v>507220</v>
       </c>
       <c r="R38" t="n">
-        <v>7053483</v>
+        <v>7053559</v>
       </c>
       <c r="S38" t="n">
         <v>8</v>
@@ -5461,6 +5456,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5487,12 +5487,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123584853</v>
+        <v>123587292</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507238</v>
+        <v>507134</v>
       </c>
       <c r="R39" t="n">
-        <v>7053518</v>
+        <v>7053449</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123583184</v>
+        <v>123585385</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -5671,19 +5671,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507077</v>
+        <v>507169</v>
       </c>
       <c r="R40" t="n">
-        <v>7053510</v>
+        <v>7053461</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5764,7 +5769,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123585385</v>
+        <v>123591099</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5798,24 +5803,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507169</v>
+        <v>506907</v>
       </c>
       <c r="R41" t="n">
-        <v>7053461</v>
+        <v>7053220</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123576823</v>
+        <v>123586717</v>
       </c>
       <c r="B42" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5908,46 +5908,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506940</v>
+        <v>507076</v>
       </c>
       <c r="R42" t="n">
-        <v>7053366</v>
+        <v>7053414</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5979,11 +5974,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6000,22 +5990,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6033,10 +6023,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123591258</v>
+        <v>123587645</v>
       </c>
       <c r="B43" t="n">
-        <v>100257</v>
+        <v>57861</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6049,27 +6039,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6078,13 +6082,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506882</v>
+        <v>507096</v>
       </c>
       <c r="R43" t="n">
-        <v>7053247</v>
+        <v>7053337</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6114,6 +6118,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6145,10 +6154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123579984</v>
+        <v>123585825</v>
       </c>
       <c r="B44" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6161,21 +6170,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6190,10 +6199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507018</v>
+        <v>507140</v>
       </c>
       <c r="R44" t="n">
-        <v>7053429</v>
+        <v>7053422</v>
       </c>
       <c r="S44" t="n">
         <v>9</v>
@@ -6277,10 +6286,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123585014</v>
+        <v>123582759</v>
       </c>
       <c r="B45" t="n">
-        <v>91678</v>
+        <v>91008</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6289,28 +6298,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -6322,13 +6340,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507278</v>
+        <v>507054</v>
       </c>
       <c r="R45" t="n">
-        <v>7053515</v>
+        <v>7053507</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6386,12 +6404,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6409,10 +6427,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123587645</v>
+        <v>123576823</v>
       </c>
       <c r="B46" t="n">
-        <v>57861</v>
+        <v>79898</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6425,41 +6443,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6468,13 +6472,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507096</v>
+        <v>506940</v>
       </c>
       <c r="R46" t="n">
-        <v>7053337</v>
+        <v>7053366</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6508,7 +6512,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6523,6 +6527,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6540,10 +6564,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123585185</v>
+        <v>123580416</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6556,27 +6580,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6585,13 +6609,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507197</v>
+        <v>507047</v>
       </c>
       <c r="R47" t="n">
-        <v>7053490</v>
+        <v>7053451</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6649,12 +6673,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6672,10 +6696,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123589530</v>
+        <v>123585702</v>
       </c>
       <c r="B48" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6684,46 +6708,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507044</v>
+        <v>507157</v>
       </c>
       <c r="R48" t="n">
-        <v>7053131</v>
+        <v>7053405</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6755,6 +6774,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6767,6 +6791,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6784,10 +6828,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123579557</v>
+        <v>123584853</v>
       </c>
       <c r="B49" t="n">
-        <v>100257</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6796,46 +6840,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507035</v>
+        <v>507238</v>
       </c>
       <c r="R49" t="n">
-        <v>7053385</v>
+        <v>7053518</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6875,6 +6914,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6891,7 +6955,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123583817</v>
+        <v>123589076</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -6925,24 +6989,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507164</v>
+        <v>507050</v>
       </c>
       <c r="R50" t="n">
-        <v>7053542</v>
+        <v>7053220</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7023,10 +7082,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123583252</v>
+        <v>123579557</v>
       </c>
       <c r="B51" t="n">
-        <v>79869</v>
+        <v>100257</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7035,31 +7094,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7068,10 +7127,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507086</v>
+        <v>507035</v>
       </c>
       <c r="R51" t="n">
-        <v>7053520</v>
+        <v>7053385</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -7114,31 +7173,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -7155,7 +7189,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123581420</v>
+        <v>123583498</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -7195,10 +7229,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507128</v>
+        <v>507170</v>
       </c>
       <c r="R52" t="n">
-        <v>7053537</v>
+        <v>7053530</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -7259,12 +7293,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7282,10 +7316,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123576777</v>
+        <v>123589530</v>
       </c>
       <c r="B53" t="n">
-        <v>79869</v>
+        <v>96957</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7294,41 +7328,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506942</v>
+        <v>507044</v>
       </c>
       <c r="R53" t="n">
-        <v>7053366</v>
+        <v>7053131</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7360,11 +7399,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7377,26 +7411,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7414,10 +7428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123582871</v>
+        <v>123585014</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7426,41 +7440,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507066</v>
+        <v>507278</v>
       </c>
       <c r="R54" t="n">
-        <v>7053479</v>
+        <v>7053515</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7518,12 +7537,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7541,7 +7560,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123586717</v>
+        <v>123585102</v>
       </c>
       <c r="B55" t="n">
         <v>78788</v>
@@ -7581,13 +7600,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507076</v>
+        <v>507242</v>
       </c>
       <c r="R55" t="n">
-        <v>7053414</v>
+        <v>7053471</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7645,12 +7664,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7668,10 +7687,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123587292</v>
+        <v>123580202</v>
       </c>
       <c r="B56" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7680,41 +7699,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507134</v>
+        <v>507014</v>
       </c>
       <c r="R56" t="n">
-        <v>7053449</v>
+        <v>7053440</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7762,22 +7786,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7795,10 +7819,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123585702</v>
+        <v>123576626</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7811,34 +7835,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507157</v>
+        <v>506978</v>
       </c>
       <c r="R57" t="n">
-        <v>7053405</v>
+        <v>7053390</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -7873,11 +7902,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7904,12 +7928,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7927,7 +7951,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123585102</v>
+        <v>123585185</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -7961,19 +7985,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507242</v>
+        <v>507197</v>
       </c>
       <c r="R58" t="n">
-        <v>7053471</v>
+        <v>7053490</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8054,7 +8083,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123589076</v>
+        <v>123583373</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -8088,19 +8117,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507050</v>
+        <v>507115</v>
       </c>
       <c r="R59" t="n">
-        <v>7053220</v>
+        <v>7053507</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8158,12 +8192,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8181,10 +8215,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123577978</v>
+        <v>123577656</v>
       </c>
       <c r="B60" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8197,42 +8231,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506936</v>
+        <v>506944</v>
       </c>
       <c r="R60" t="n">
-        <v>7053351</v>
+        <v>7053309</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8290,12 +8319,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8313,10 +8342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123582759</v>
+        <v>123583817</v>
       </c>
       <c r="B61" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8329,36 +8358,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8367,13 +8387,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507054</v>
+        <v>507164</v>
       </c>
       <c r="R61" t="n">
-        <v>7053507</v>
+        <v>7053542</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8431,12 +8451,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8454,10 +8474,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123577590</v>
+        <v>123577978</v>
       </c>
       <c r="B62" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8470,32 +8490,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8504,13 +8519,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506932</v>
+        <v>506936</v>
       </c>
       <c r="R62" t="n">
-        <v>7053304</v>
+        <v>7053351</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8542,11 +8557,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8573,12 +8583,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8596,10 +8606,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123576556</v>
+        <v>123586447</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8612,37 +8622,51 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506963</v>
+        <v>507120</v>
       </c>
       <c r="R63" t="n">
-        <v>7053384</v>
+        <v>7053421</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8674,6 +8698,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8686,26 +8715,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8723,10 +8732,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123586447</v>
+        <v>123579984</v>
       </c>
       <c r="B64" t="n">
-        <v>57644</v>
+        <v>90986</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8739,51 +8748,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507120</v>
+        <v>507018</v>
       </c>
       <c r="R64" t="n">
-        <v>7053421</v>
+        <v>7053429</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8815,11 +8815,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8832,6 +8827,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8849,10 +8864,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123588146</v>
+        <v>123577798</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8865,34 +8880,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507059</v>
+        <v>506927</v>
       </c>
       <c r="R65" t="n">
-        <v>7053347</v>
+        <v>7053299</v>
       </c>
       <c r="S65" t="n">
         <v>9</v>
@@ -8943,22 +8963,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8976,10 +8996,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123583498</v>
+        <v>123579440</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8988,41 +9008,46 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507170</v>
+        <v>507010</v>
       </c>
       <c r="R66" t="n">
-        <v>7053530</v>
+        <v>7053401</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9062,31 +9087,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -9240,10 +9240,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123772501</v>
+        <v>123580751</v>
       </c>
       <c r="B68" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9256,44 +9256,47 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507174</v>
+        <v>507106</v>
       </c>
       <c r="R68" t="n">
-        <v>7053322</v>
+        <v>7053481</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9317,12 +9320,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9331,7 +9339,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9340,11 +9347,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ68" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9357,12 +9359,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9380,10 +9382,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123772770</v>
+        <v>123579421</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9396,40 +9398,47 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507241</v>
+        <v>507014</v>
       </c>
       <c r="R69" t="n">
-        <v>7053498</v>
+        <v>7053420</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9453,17 +9462,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9472,7 +9481,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9493,12 +9501,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9658,10 +9666,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123580751</v>
+        <v>123772501</v>
       </c>
       <c r="B71" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9674,47 +9682,44 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507106</v>
+        <v>507174</v>
       </c>
       <c r="R71" t="n">
-        <v>7053481</v>
+        <v>7053322</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9738,17 +9743,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9757,6 +9757,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9765,6 +9766,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ71" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9777,12 +9783,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9800,10 +9806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123590101</v>
+        <v>123772770</v>
       </c>
       <c r="B72" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9816,47 +9822,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507030</v>
+        <v>507241</v>
       </c>
       <c r="R72" t="n">
-        <v>7053146</v>
+        <v>7053498</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9880,17 +9879,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9899,6 +9898,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9919,12 +9919,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123590902</v>
+        <v>123590101</v>
       </c>
       <c r="B73" t="n">
         <v>57491</v>
@@ -9992,10 +9992,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506945</v>
+        <v>507030</v>
       </c>
       <c r="R73" t="n">
-        <v>7053117</v>
+        <v>7053146</v>
       </c>
       <c r="S73" t="n">
         <v>7</v>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10084,7 +10084,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123579421</v>
+        <v>123590902</v>
       </c>
       <c r="B74" t="n">
         <v>57491</v>
@@ -10134,13 +10134,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507014</v>
+        <v>506945</v>
       </c>
       <c r="R74" t="n">
-        <v>7053420</v>
+        <v>7053117</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123588776</v>
+        <v>123591258</v>
       </c>
       <c r="B27" t="n">
-        <v>79870</v>
+        <v>100257</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3968,31 +3968,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507044</v>
+        <v>506882</v>
       </c>
       <c r="R27" t="n">
-        <v>7053321</v>
+        <v>7053247</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4039,11 +4039,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4056,26 +4051,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4093,10 +4068,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123583184</v>
+        <v>123588776</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4109,34 +4084,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507077</v>
+        <v>507044</v>
       </c>
       <c r="R28" t="n">
-        <v>7053510</v>
+        <v>7053321</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4171,6 +4151,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4187,22 +4172,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4220,10 +4205,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123591258</v>
+        <v>123583184</v>
       </c>
       <c r="B29" t="n">
-        <v>100257</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4232,46 +4217,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506882</v>
+        <v>507077</v>
       </c>
       <c r="R29" t="n">
-        <v>7053247</v>
+        <v>7053510</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4315,6 +4295,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123584458</v>
+        <v>123587292</v>
       </c>
       <c r="B38" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5385,43 +5385,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507220</v>
+        <v>507134</v>
       </c>
       <c r="R38" t="n">
-        <v>7053559</v>
+        <v>7053449</v>
       </c>
       <c r="S38" t="n">
         <v>8</v>
@@ -5456,11 +5451,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5487,12 +5477,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5510,10 +5500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123587292</v>
+        <v>123584458</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5522,38 +5512,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507134</v>
+        <v>507220</v>
       </c>
       <c r="R39" t="n">
-        <v>7053449</v>
+        <v>7053559</v>
       </c>
       <c r="S39" t="n">
         <v>8</v>
@@ -5588,6 +5583,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5614,12 +5614,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123586717</v>
+        <v>123587645</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5908,41 +5908,60 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507076</v>
+        <v>507096</v>
       </c>
       <c r="R42" t="n">
-        <v>7053414</v>
+        <v>7053337</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5974,6 +5993,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5986,26 +6010,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6023,10 +6027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123587645</v>
+        <v>123586717</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6035,60 +6039,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507096</v>
+        <v>507076</v>
       </c>
       <c r="R43" t="n">
-        <v>7053337</v>
+        <v>7053414</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6120,11 +6105,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6137,6 +6117,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -7189,10 +7189,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123583498</v>
+        <v>123585014</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7201,41 +7201,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507170</v>
+        <v>507278</v>
       </c>
       <c r="R52" t="n">
-        <v>7053530</v>
+        <v>7053515</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7293,12 +7298,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7316,10 +7321,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123589530</v>
+        <v>123583498</v>
       </c>
       <c r="B53" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7328,46 +7333,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507044</v>
+        <v>507170</v>
       </c>
       <c r="R53" t="n">
-        <v>7053131</v>
+        <v>7053530</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7411,6 +7411,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7428,10 +7448,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123585014</v>
+        <v>123589530</v>
       </c>
       <c r="B54" t="n">
-        <v>91678</v>
+        <v>96957</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7444,27 +7464,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7473,13 +7493,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507278</v>
+        <v>507044</v>
       </c>
       <c r="R54" t="n">
-        <v>7053515</v>
+        <v>7053131</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7523,26 +7543,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123591258</v>
+        <v>123579984</v>
       </c>
       <c r="B27" t="n">
-        <v>100257</v>
+        <v>90986</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3968,31 +3968,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506882</v>
+        <v>507018</v>
       </c>
       <c r="R27" t="n">
-        <v>7053247</v>
+        <v>7053429</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4051,6 +4051,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4068,10 +4088,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123588776</v>
+        <v>123577590</v>
       </c>
       <c r="B28" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4084,27 +4104,32 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4113,13 +4138,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507044</v>
+        <v>506932</v>
       </c>
       <c r="R28" t="n">
-        <v>7053321</v>
+        <v>7053304</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4153,7 +4178,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4172,22 +4197,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4205,7 +4230,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123583184</v>
+        <v>123588146</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -4245,10 +4270,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507077</v>
+        <v>507059</v>
       </c>
       <c r="R29" t="n">
-        <v>7053510</v>
+        <v>7053347</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -4332,7 +4357,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123581420</v>
+        <v>123585702</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -4372,10 +4397,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507128</v>
+        <v>507157</v>
       </c>
       <c r="R30" t="n">
-        <v>7053537</v>
+        <v>7053405</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4408,6 +4433,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4459,7 +4489,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123582871</v>
+        <v>123581420</v>
       </c>
       <c r="B31" t="n">
         <v>78788</v>
@@ -4499,13 +4529,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507066</v>
+        <v>507128</v>
       </c>
       <c r="R31" t="n">
-        <v>7053479</v>
+        <v>7053537</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4586,10 +4616,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123580927</v>
+        <v>123584458</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4598,38 +4628,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507115</v>
+        <v>507220</v>
       </c>
       <c r="R32" t="n">
-        <v>7053483</v>
+        <v>7053559</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4664,6 +4699,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4690,12 +4730,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4713,10 +4753,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123577590</v>
+        <v>123583252</v>
       </c>
       <c r="B33" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4729,32 +4769,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4763,13 +4798,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506932</v>
+        <v>507086</v>
       </c>
       <c r="R33" t="n">
-        <v>7053304</v>
+        <v>7053520</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4801,11 +4836,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4822,22 +4852,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4855,10 +4885,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123576777</v>
+        <v>123585385</v>
       </c>
       <c r="B34" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4871,37 +4901,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506942</v>
+        <v>507169</v>
       </c>
       <c r="R34" t="n">
-        <v>7053366</v>
+        <v>7053461</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4933,11 +4968,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4954,22 +4984,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4987,10 +5017,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123583252</v>
+        <v>123576823</v>
       </c>
       <c r="B35" t="n">
-        <v>79869</v>
+        <v>79898</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4999,31 +5029,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5032,13 +5062,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507086</v>
+        <v>506940</v>
       </c>
       <c r="R35" t="n">
-        <v>7053520</v>
+        <v>7053366</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5068,6 +5098,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5119,10 +5154,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123576556</v>
+        <v>123587645</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5131,41 +5166,60 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506963</v>
+        <v>507096</v>
       </c>
       <c r="R36" t="n">
-        <v>7053384</v>
+        <v>7053337</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5197,6 +5251,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5209,26 +5268,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5246,10 +5285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123588146</v>
+        <v>123589530</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5258,41 +5297,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507059</v>
+        <v>507044</v>
       </c>
       <c r="R37" t="n">
-        <v>7053347</v>
+        <v>7053131</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5336,26 +5380,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5373,10 +5397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123587292</v>
+        <v>123585825</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5389,37 +5413,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507134</v>
+        <v>507140</v>
       </c>
       <c r="R38" t="n">
-        <v>7053449</v>
+        <v>7053422</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5477,12 +5506,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5500,10 +5529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123584458</v>
+        <v>123583184</v>
       </c>
       <c r="B39" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5512,46 +5541,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507220</v>
+        <v>507077</v>
       </c>
       <c r="R39" t="n">
-        <v>7053559</v>
+        <v>7053510</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5583,11 +5607,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5614,12 +5633,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5637,7 +5656,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123585385</v>
+        <v>123583817</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -5682,13 +5701,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507169</v>
+        <v>507164</v>
       </c>
       <c r="R40" t="n">
-        <v>7053461</v>
+        <v>7053542</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5769,7 +5788,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123591099</v>
+        <v>123583498</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5809,10 +5828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506907</v>
+        <v>507170</v>
       </c>
       <c r="R41" t="n">
-        <v>7053220</v>
+        <v>7053530</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5873,12 +5892,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5896,10 +5915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123587645</v>
+        <v>123586447</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5908,40 +5927,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5951,17 +5965,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507096</v>
+        <v>507120</v>
       </c>
       <c r="R42" t="n">
-        <v>7053337</v>
+        <v>7053421</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5995,7 +6009,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6027,10 +6041,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123586717</v>
+        <v>123580416</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6043,37 +6057,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507076</v>
+        <v>507047</v>
       </c>
       <c r="R43" t="n">
-        <v>7053414</v>
+        <v>7053451</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6131,12 +6150,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6154,10 +6173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123585825</v>
+        <v>123584853</v>
       </c>
       <c r="B44" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6170,42 +6189,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507140</v>
+        <v>507238</v>
       </c>
       <c r="R44" t="n">
-        <v>7053422</v>
+        <v>7053518</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6263,12 +6277,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6286,10 +6300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123582759</v>
+        <v>123576777</v>
       </c>
       <c r="B45" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6302,51 +6316,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507054</v>
+        <v>506942</v>
       </c>
       <c r="R45" t="n">
-        <v>7053507</v>
+        <v>7053366</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6378,6 +6378,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6394,22 +6399,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6427,10 +6432,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123576823</v>
+        <v>123576556</v>
       </c>
       <c r="B46" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6439,46 +6444,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506940</v>
+        <v>506963</v>
       </c>
       <c r="R46" t="n">
-        <v>7053366</v>
+        <v>7053384</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6510,11 +6510,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6531,22 +6526,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6564,10 +6559,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123580416</v>
+        <v>123577656</v>
       </c>
       <c r="B47" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6580,42 +6575,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507047</v>
+        <v>506944</v>
       </c>
       <c r="R47" t="n">
-        <v>7053451</v>
+        <v>7053309</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6673,12 +6663,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6696,10 +6686,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123585702</v>
+        <v>123580202</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6708,41 +6698,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507157</v>
+        <v>507014</v>
       </c>
       <c r="R48" t="n">
-        <v>7053405</v>
+        <v>7053440</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6774,11 +6769,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6795,22 +6785,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6828,7 +6818,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123584853</v>
+        <v>123585102</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -6868,13 +6858,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507238</v>
+        <v>507242</v>
       </c>
       <c r="R49" t="n">
-        <v>7053518</v>
+        <v>7053471</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6955,7 +6945,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123589076</v>
+        <v>123582871</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -6995,13 +6985,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507050</v>
+        <v>507066</v>
       </c>
       <c r="R50" t="n">
-        <v>7053220</v>
+        <v>7053479</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7082,10 +7072,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123579557</v>
+        <v>123589076</v>
       </c>
       <c r="B51" t="n">
-        <v>100257</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7094,46 +7084,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507035</v>
+        <v>507050</v>
       </c>
       <c r="R51" t="n">
-        <v>7053385</v>
+        <v>7053220</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7173,6 +7158,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -7189,10 +7199,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123585014</v>
+        <v>123588776</v>
       </c>
       <c r="B52" t="n">
-        <v>91678</v>
+        <v>79870</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7201,31 +7211,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7234,13 +7244,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507278</v>
+        <v>507044</v>
       </c>
       <c r="R52" t="n">
-        <v>7053515</v>
+        <v>7053321</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7272,6 +7282,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7288,22 +7303,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7321,10 +7336,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123583498</v>
+        <v>123579440</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7333,41 +7348,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507170</v>
+        <v>507010</v>
       </c>
       <c r="R53" t="n">
-        <v>7053530</v>
+        <v>7053401</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7407,31 +7427,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7448,10 +7443,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123589530</v>
+        <v>123580927</v>
       </c>
       <c r="B54" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7460,46 +7455,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507044</v>
+        <v>507115</v>
       </c>
       <c r="R54" t="n">
-        <v>7053131</v>
+        <v>7053483</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7543,6 +7533,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7560,7 +7570,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123585102</v>
+        <v>123591099</v>
       </c>
       <c r="B55" t="n">
         <v>78788</v>
@@ -7600,13 +7610,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507242</v>
+        <v>506907</v>
       </c>
       <c r="R55" t="n">
-        <v>7053471</v>
+        <v>7053220</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7687,10 +7697,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123580202</v>
+        <v>123583373</v>
       </c>
       <c r="B56" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7699,25 +7709,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7732,13 +7742,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507014</v>
+        <v>507115</v>
       </c>
       <c r="R56" t="n">
-        <v>7053440</v>
+        <v>7053507</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7786,22 +7796,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7951,10 +7961,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123585185</v>
+        <v>123591258</v>
       </c>
       <c r="B58" t="n">
-        <v>78788</v>
+        <v>100257</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7963,31 +7973,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7996,13 +8006,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507197</v>
+        <v>506882</v>
       </c>
       <c r="R58" t="n">
-        <v>7053490</v>
+        <v>7053247</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8046,26 +8056,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8083,10 +8073,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123583373</v>
+        <v>123582759</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8099,27 +8089,36 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8128,13 +8127,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507115</v>
+        <v>507054</v>
       </c>
       <c r="R59" t="n">
         <v>7053507</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8192,12 +8191,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8215,7 +8214,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123577656</v>
+        <v>123587292</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -8255,13 +8254,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506944</v>
+        <v>507134</v>
       </c>
       <c r="R60" t="n">
-        <v>7053309</v>
+        <v>7053449</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8342,10 +8341,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123583817</v>
+        <v>123579557</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>100257</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8354,31 +8353,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8387,10 +8386,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507164</v>
+        <v>507035</v>
       </c>
       <c r="R61" t="n">
-        <v>7053542</v>
+        <v>7053385</v>
       </c>
       <c r="S61" t="n">
         <v>9</v>
@@ -8433,31 +8432,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8474,10 +8448,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123577978</v>
+        <v>123577798</v>
       </c>
       <c r="B62" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8490,27 +8464,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8519,13 +8493,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506936</v>
+        <v>506927</v>
       </c>
       <c r="R62" t="n">
-        <v>7053351</v>
+        <v>7053299</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8573,22 +8547,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8606,10 +8580,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123586447</v>
+        <v>123586717</v>
       </c>
       <c r="B63" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8622,51 +8596,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507120</v>
+        <v>507076</v>
       </c>
       <c r="R63" t="n">
-        <v>7053421</v>
+        <v>7053414</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8698,11 +8658,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8715,6 +8670,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8732,10 +8707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123579984</v>
+        <v>123585014</v>
       </c>
       <c r="B64" t="n">
-        <v>90986</v>
+        <v>91678</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8744,25 +8719,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8777,13 +8752,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507018</v>
+        <v>507278</v>
       </c>
       <c r="R64" t="n">
-        <v>7053429</v>
+        <v>7053515</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8864,10 +8839,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123577798</v>
+        <v>123577978</v>
       </c>
       <c r="B65" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8880,27 +8855,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8909,13 +8884,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506927</v>
+        <v>506936</v>
       </c>
       <c r="R65" t="n">
-        <v>7053299</v>
+        <v>7053351</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8963,22 +8938,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8996,10 +8971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123579440</v>
+        <v>123585185</v>
       </c>
       <c r="B66" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9008,31 +8983,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9041,13 +9016,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>507010</v>
+        <v>507197</v>
       </c>
       <c r="R66" t="n">
-        <v>7053401</v>
+        <v>7053490</v>
       </c>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9087,6 +9062,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -9103,10 +9103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123581252</v>
+        <v>123772770</v>
       </c>
       <c r="B67" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9119,42 +9119,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507113</v>
+        <v>507241</v>
       </c>
       <c r="R67" t="n">
-        <v>7053527</v>
+        <v>7053498</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9178,17 +9176,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9197,6 +9195,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9207,22 +9206,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9240,7 +9239,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123580751</v>
+        <v>123590101</v>
       </c>
       <c r="B68" t="n">
         <v>57491</v>
@@ -9276,7 +9275,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9290,13 +9289,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507106</v>
+        <v>507030</v>
       </c>
       <c r="R68" t="n">
-        <v>7053481</v>
+        <v>7053146</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9330,7 +9329,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9382,10 +9381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123579421</v>
+        <v>123581252</v>
       </c>
       <c r="B69" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9398,32 +9397,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9432,13 +9426,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507014</v>
+        <v>507113</v>
       </c>
       <c r="R69" t="n">
-        <v>7053420</v>
+        <v>7053527</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9472,7 +9466,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9491,22 +9485,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9524,7 +9518,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123588546</v>
+        <v>123579421</v>
       </c>
       <c r="B70" t="n">
         <v>57491</v>
@@ -9560,7 +9554,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9574,13 +9568,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507024</v>
+        <v>507014</v>
       </c>
       <c r="R70" t="n">
-        <v>7053316</v>
+        <v>7053420</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9614,7 +9608,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9666,10 +9660,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123772501</v>
+        <v>123580751</v>
       </c>
       <c r="B71" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9682,44 +9676,47 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507174</v>
+        <v>507106</v>
       </c>
       <c r="R71" t="n">
-        <v>7053322</v>
+        <v>7053481</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9743,12 +9740,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9757,7 +9759,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9766,11 +9767,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ71" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9783,12 +9779,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9806,10 +9802,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123772770</v>
+        <v>123590902</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9822,40 +9818,47 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507241</v>
+        <v>506945</v>
       </c>
       <c r="R72" t="n">
-        <v>7053498</v>
+        <v>7053117</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9879,17 +9882,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9898,7 +9901,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9919,12 +9921,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9942,10 +9944,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123590101</v>
+        <v>123772501</v>
       </c>
       <c r="B73" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9958,47 +9960,44 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507030</v>
+        <v>507174</v>
       </c>
       <c r="R73" t="n">
-        <v>7053146</v>
+        <v>7053322</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10022,17 +10021,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10041,6 +10035,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10049,6 +10044,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ73" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123590902</v>
+        <v>123582066</v>
       </c>
       <c r="B74" t="n">
         <v>57491</v>
@@ -10134,13 +10134,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506945</v>
+        <v>507073</v>
       </c>
       <c r="R74" t="n">
-        <v>7053117</v>
+        <v>7053530</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10226,7 +10226,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123582066</v>
+        <v>123588546</v>
       </c>
       <c r="B75" t="n">
         <v>57491</v>
@@ -10262,7 +10262,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507073</v>
+        <v>507024</v>
       </c>
       <c r="R75" t="n">
-        <v>7053530</v>
+        <v>7053316</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -9103,10 +9103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123582066</v>
+        <v>123772770</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9119,47 +9119,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507073</v>
+        <v>507241</v>
       </c>
       <c r="R67" t="n">
-        <v>7053530</v>
+        <v>7053498</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9183,17 +9176,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9202,6 +9195,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9222,12 +9216,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9245,7 +9239,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123588546</v>
+        <v>123579421</v>
       </c>
       <c r="B68" t="n">
         <v>57513</v>
@@ -9281,7 +9275,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9295,13 +9289,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507024</v>
+        <v>507014</v>
       </c>
       <c r="R68" t="n">
-        <v>7053316</v>
+        <v>7053420</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9335,7 +9329,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9387,10 +9381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123772501</v>
+        <v>123582066</v>
       </c>
       <c r="B69" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9403,44 +9397,47 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507174</v>
+        <v>507073</v>
       </c>
       <c r="R69" t="n">
-        <v>7053322</v>
+        <v>7053530</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9464,12 +9461,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9478,7 +9480,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9487,11 +9488,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AJ69" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9504,12 +9500,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9527,10 +9523,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123772770</v>
+        <v>123772501</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9543,26 +9539,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507241</v>
+        <v>507174</v>
       </c>
       <c r="R70" t="n">
-        <v>7053498</v>
+        <v>7053322</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9608,11 +9608,6 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +9623,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AJ70" t="inlineStr">
         <is>
           <t>gran</t>
@@ -9640,12 +9640,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9663,10 +9663,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123590902</v>
+        <v>123581252</v>
       </c>
       <c r="B71" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9679,32 +9679,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9713,13 +9708,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506945</v>
+        <v>507113</v>
       </c>
       <c r="R71" t="n">
-        <v>7053117</v>
+        <v>7053527</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9753,7 +9748,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9772,22 +9767,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9805,10 +9800,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123581252</v>
+        <v>123590902</v>
       </c>
       <c r="B72" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9821,27 +9816,32 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9850,13 +9850,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507113</v>
+        <v>506945</v>
       </c>
       <c r="R72" t="n">
-        <v>7053527</v>
+        <v>7053117</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9909,22 +9909,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123579421</v>
+        <v>123580751</v>
       </c>
       <c r="B73" t="n">
         <v>57513</v>
@@ -9978,7 +9978,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -9992,10 +9992,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507014</v>
+        <v>507106</v>
       </c>
       <c r="R73" t="n">
-        <v>7053420</v>
+        <v>7053481</v>
       </c>
       <c r="S73" t="n">
         <v>9</v>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10084,7 +10084,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123590101</v>
+        <v>123588546</v>
       </c>
       <c r="B74" t="n">
         <v>57513</v>
@@ -10120,7 +10120,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10134,13 +10134,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507030</v>
+        <v>507024</v>
       </c>
       <c r="R74" t="n">
-        <v>7053146</v>
+        <v>7053316</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10226,7 +10226,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123580751</v>
+        <v>123590101</v>
       </c>
       <c r="B75" t="n">
         <v>57513</v>
@@ -10262,7 +10262,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507106</v>
+        <v>507030</v>
       </c>
       <c r="R75" t="n">
-        <v>7053481</v>
+        <v>7053146</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90798960</v>
+        <v>122779265</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506886.1700459546</v>
+        <v>507188</v>
       </c>
       <c r="R2" t="n">
-        <v>7053241.935609749</v>
+        <v>7053524</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,52 +761,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Möjlig kalkbarrskog</t>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Grov sälg</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90798965</v>
+        <v>123579984</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,37 +816,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506930.9035939532</v>
+        <v>507018</v>
       </c>
       <c r="R3" t="n">
-        <v>7053363.947876468</v>
+        <v>7053429</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,87 +892,93 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Grov sälg</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91131085</v>
+        <v>123580416</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506914.8908245256</v>
+        <v>507047</v>
       </c>
       <c r="R4" t="n">
-        <v>7053351.899631883</v>
+        <v>7053451</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,22 +1002,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,82 +1019,93 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91131051</v>
+        <v>123588776</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507126.1359057049</v>
+        <v>507044</v>
       </c>
       <c r="R5" t="n">
-        <v>7053521.883973744</v>
+        <v>7053321</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1129,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en lutande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,44 +1151,50 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91131081</v>
+        <v>123584458</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,37 +1202,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506990.0880336461</v>
+        <v>507220</v>
       </c>
       <c r="R6" t="n">
-        <v>7053396.112983297</v>
+        <v>7053559</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,22 +1261,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer i en relativt nyligen fallen död gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,44 +1283,50 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91131071</v>
+        <v>123585014</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,37 +1334,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507113.8094526606</v>
+        <v>507278</v>
       </c>
       <c r="R7" t="n">
-        <v>7053456.008319411</v>
+        <v>7053515</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,22 +1393,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,82 +1410,91 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91131054</v>
+        <v>122779331</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507014.0517798079</v>
+        <v>507003</v>
       </c>
       <c r="R8" t="n">
-        <v>7053438.879038485</v>
+        <v>7053201</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,22 +1518,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,85 +1537,92 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91131061</v>
+        <v>123576556</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506899.8599620049</v>
+        <v>506963</v>
       </c>
       <c r="R9" t="n">
-        <v>7053298.028967588</v>
+        <v>7053384</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1637,22 +1646,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,82 +1663,88 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91131079</v>
+        <v>123577656</v>
       </c>
       <c r="B10" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506909.9408634785</v>
+        <v>506944</v>
       </c>
       <c r="R10" t="n">
-        <v>7053169.904056957</v>
+        <v>7053309</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1763,22 +1768,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,82 +1785,88 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91131070</v>
+        <v>123580927</v>
       </c>
       <c r="B11" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507113.8094526606</v>
+        <v>507115</v>
       </c>
       <c r="R11" t="n">
-        <v>7053456.008319411</v>
+        <v>7053483</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1889,22 +1890,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,82 +1907,88 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91131055</v>
+        <v>123581420</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507014.0517798079</v>
+        <v>507128</v>
       </c>
       <c r="R12" t="n">
-        <v>7053438.879038485</v>
+        <v>7053537</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2015,22 +2012,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2042,82 +2029,93 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91131080</v>
+        <v>123582390</v>
       </c>
       <c r="B13" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506990.0880336461</v>
+        <v>507079</v>
       </c>
       <c r="R13" t="n">
-        <v>7053396.112983297</v>
+        <v>7053561</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2141,22 +2139,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Relativt gott om garnlav på flertalet granar i gammal granskog. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,82 +2161,88 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91131069</v>
+        <v>123582871</v>
       </c>
       <c r="B14" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507113.8094526606</v>
+        <v>507066</v>
       </c>
       <c r="R14" t="n">
-        <v>7053456.008319411</v>
+        <v>7053479</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2267,22 +2266,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2294,82 +2283,88 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91131050</v>
+        <v>123583184</v>
       </c>
       <c r="B15" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507126.1359057049</v>
+        <v>507077</v>
       </c>
       <c r="R15" t="n">
-        <v>7053521.883973744</v>
+        <v>7053510</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2393,22 +2388,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2420,82 +2405,93 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91131075</v>
+        <v>123583373</v>
       </c>
       <c r="B16" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507047.1694520126</v>
+        <v>507115</v>
       </c>
       <c r="R16" t="n">
-        <v>7053171.095845994</v>
+        <v>7053507</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2519,22 +2515,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2546,82 +2532,88 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>91131044</v>
+        <v>123583498</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507105.8420044744</v>
+        <v>507170</v>
       </c>
       <c r="R17" t="n">
-        <v>7053233.965921329</v>
+        <v>7053530</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2645,22 +2637,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2672,94 +2654,93 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Andreas Karlsson Tiselius</t>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122779043</v>
+        <v>123583817</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507225</v>
+        <v>507164</v>
       </c>
       <c r="R18" t="n">
-        <v>7053395</v>
+        <v>7053542</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2783,17 +2764,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med både färska och äldre ringhack längs ca 6 meter på en granstam. I skogsbeståndet där fyndplatsen ligger finns partier med stående död ved som indikerar medelhöga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym död ved.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2810,11 +2786,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2827,12 +2798,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2850,19 +2821,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122779331</v>
+        <v>123584853</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2884,22 +2850,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507003</v>
+        <v>507238</v>
       </c>
       <c r="R19" t="n">
-        <v>7053201</v>
+        <v>7053518</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2923,17 +2886,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2942,13 +2900,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2986,60 +2943,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122779272</v>
+        <v>123585102</v>
       </c>
       <c r="B20" t="n">
-        <v>90984</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507186</v>
+        <v>507242</v>
       </c>
       <c r="R20" t="n">
-        <v>7053514</v>
+        <v>7053471</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3063,12 +3008,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3077,7 +3022,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3086,11 +3030,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3103,12 +3042,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3126,60 +3065,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122779282</v>
+        <v>123585185</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>med apothecier</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507098</v>
+        <v>507197</v>
       </c>
       <c r="R21" t="n">
-        <v>7053554</v>
+        <v>7053490</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3203,17 +3135,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gott om luddlav intill lunglav på en sälg.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3222,7 +3149,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3231,29 +3157,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3271,60 +3192,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122779318</v>
+        <v>123585385</v>
       </c>
       <c r="B22" t="n">
-        <v>79856</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>med apothecier</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507101</v>
+        <v>507169</v>
       </c>
       <c r="R22" t="n">
-        <v>7053264</v>
+        <v>7053461</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3348,17 +3262,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på rönn.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3367,7 +3276,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3376,29 +3284,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3416,60 +3319,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122779265</v>
+        <v>123585702</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507188</v>
+        <v>507157</v>
       </c>
       <c r="R23" t="n">
-        <v>7053524</v>
+        <v>7053405</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3493,12 +3384,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3507,7 +3403,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3516,11 +3411,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3531,9 +3421,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3551,60 +3446,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122779277</v>
+        <v>123586717</v>
       </c>
       <c r="B24" t="n">
-        <v>79856</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507098</v>
+        <v>507076</v>
       </c>
       <c r="R24" t="n">
-        <v>7053554</v>
+        <v>7053414</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3628,17 +3511,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på sälg.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3647,7 +3525,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3658,22 +3535,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3691,61 +3568,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122779296</v>
+        <v>123587292</v>
       </c>
       <c r="B25" t="n">
-        <v>56683</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507257</v>
+        <v>507134</v>
       </c>
       <c r="R25" t="n">
-        <v>7053479</v>
+        <v>7053449</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3769,17 +3633,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3796,9 +3655,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Gammal grandominerad skog.</t>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3816,61 +3690,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122779298</v>
+        <v>123588146</v>
       </c>
       <c r="B26" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507119</v>
+        <v>507059</v>
       </c>
       <c r="R26" t="n">
-        <v>7053255</v>
+        <v>7053347</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3894,17 +3755,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår i en gran.</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3933,12 +3789,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3956,19 +3812,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123583184</v>
+        <v>123589076</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3996,13 +3847,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507077</v>
+        <v>507050</v>
       </c>
       <c r="R27" t="n">
-        <v>7053510</v>
+        <v>7053220</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4083,58 +3934,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123580416</v>
+        <v>123591099</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507047</v>
+        <v>506907</v>
       </c>
       <c r="R28" t="n">
-        <v>7053451</v>
+        <v>7053220</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4192,12 +4033,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4215,58 +4056,51 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123577978</v>
+        <v>123772770</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506936</v>
+        <v>507241</v>
       </c>
       <c r="R29" t="n">
-        <v>7053351</v>
+        <v>7053498</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4290,12 +4124,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4304,6 +4143,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4324,12 +4164,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4347,15 +4187,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123585702</v>
+        <v>90798960</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4363,37 +4198,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507157</v>
+        <v>506886</v>
       </c>
       <c r="R30" t="n">
-        <v>7053405</v>
+        <v>7053242</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4417,17 +4252,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4439,98 +4269,82 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Grov sälg</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123579557</v>
+        <v>90798965</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507035</v>
+        <v>506931</v>
       </c>
       <c r="R31" t="n">
-        <v>7053385</v>
+        <v>7053364</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4554,12 +4368,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4570,31 +4384,45 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Grov sälg</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123587292</v>
+        <v>122779277</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4602,37 +4430,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507134</v>
+        <v>507098</v>
       </c>
       <c r="R32" t="n">
-        <v>7053449</v>
+        <v>7053554</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4656,12 +4491,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4670,6 +4510,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4680,22 +4521,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4713,15 +4554,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123581420</v>
+        <v>122779318</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4729,37 +4565,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507128</v>
+        <v>507101</v>
       </c>
       <c r="R33" t="n">
-        <v>7053537</v>
+        <v>7053264</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4783,12 +4626,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på rönn.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4797,6 +4645,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4805,24 +4654,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4840,15 +4694,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123591099</v>
+        <v>123576777</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4856,21 +4705,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4880,13 +4729,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506907</v>
+        <v>506942</v>
       </c>
       <c r="R34" t="n">
-        <v>7053220</v>
+        <v>7053366</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4918,6 +4767,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en grovbarkad sälglåga.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4934,22 +4788,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4967,43 +4821,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123591258</v>
+        <v>123577798</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5012,13 +4861,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506882</v>
+        <v>506927</v>
       </c>
       <c r="R35" t="n">
-        <v>7053247</v>
+        <v>7053299</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5062,6 +4911,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5079,15 +4948,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123585385</v>
+        <v>123580175</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5095,27 +4959,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5124,13 +4988,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507169</v>
+        <v>507012</v>
       </c>
       <c r="R36" t="n">
-        <v>7053461</v>
+        <v>7053453</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5178,22 +5042,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5211,15 +5075,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123576556</v>
+        <v>123581252</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5227,37 +5086,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506963</v>
+        <v>507113</v>
       </c>
       <c r="R37" t="n">
-        <v>7053384</v>
+        <v>7053527</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5289,6 +5153,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5305,22 +5174,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5338,15 +5207,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123586717</v>
+        <v>123583252</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5354,34 +5218,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507076</v>
+        <v>507086</v>
       </c>
       <c r="R38" t="n">
-        <v>7053414</v>
+        <v>7053520</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5432,22 +5301,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5465,15 +5334,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123583498</v>
+        <v>123591471</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5481,21 +5345,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5505,13 +5369,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507170</v>
+        <v>506865</v>
       </c>
       <c r="R39" t="n">
-        <v>7053530</v>
+        <v>7053369</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5559,22 +5423,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5592,53 +5456,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123576777</v>
+        <v>123576823</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506942</v>
+        <v>506940</v>
       </c>
       <c r="R40" t="n">
         <v>7053366</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5701,12 +5565,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5724,15 +5588,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123579440</v>
+        <v>123580239</v>
       </c>
       <c r="B41" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5740,27 +5599,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5769,13 +5628,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507010</v>
+        <v>507008</v>
       </c>
       <c r="R41" t="n">
-        <v>7053401</v>
+        <v>7053453</v>
       </c>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5815,6 +5674,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5831,53 +5715,55 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123585102</v>
+        <v>122779282</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507242</v>
+        <v>507098</v>
       </c>
       <c r="R42" t="n">
-        <v>7053471</v>
+        <v>7053554</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5901,12 +5787,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gott om luddlav intill lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5915,6 +5806,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5923,24 +5815,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5958,15 +5855,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123584458</v>
+        <v>123580202</v>
       </c>
       <c r="B43" t="n">
-        <v>91700</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5974,27 +5866,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6003,13 +5895,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507220</v>
+        <v>507014</v>
       </c>
       <c r="R43" t="n">
-        <v>7053559</v>
+        <v>7053440</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6041,11 +5933,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växer i en relativt nyligen fallen död gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6062,22 +5949,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6095,58 +5982,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123588776</v>
+        <v>122779298</v>
       </c>
       <c r="B44" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507044</v>
+        <v>507119</v>
       </c>
       <c r="R44" t="n">
-        <v>7053321</v>
+        <v>7053255</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6170,17 +6055,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en lutande sälg.</t>
+          <t>Färska rejäla hackspår i en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6199,22 +6084,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6232,15 +6117,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123576626</v>
+        <v>122779043</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6248,42 +6128,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506978</v>
+        <v>507225</v>
       </c>
       <c r="R45" t="n">
-        <v>7053390</v>
+        <v>7053395</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6307,12 +6194,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med både färska och äldre ringhack längs ca 6 meter på en granstam. I skogsbeståndet där fyndplatsen ligger finns partier med stående död ved som indikerar medelhöga till mycket höga livsmiljövärden för tretåig hackspett baserat på volym död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6329,6 +6221,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AJ45" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6341,12 +6238,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6364,15 +6261,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123577798</v>
+        <v>123576291</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6380,27 +6272,32 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6412,10 +6309,10 @@
         <v>506927</v>
       </c>
       <c r="R46" t="n">
-        <v>7053299</v>
+        <v>7053396</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6447,11 +6344,16 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett bohål möjligen efter tretåig hackspett med rund form på ca 3,5 meters  höjd i en granhögstubbe som är angripen av granticka. Kring fyndplatsen finns minst medehöga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -6463,22 +6365,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6496,15 +6398,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123583252</v>
+        <v>123577590</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6512,27 +6409,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6541,13 +6443,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507086</v>
+        <v>506932</v>
       </c>
       <c r="R47" t="n">
-        <v>7053520</v>
+        <v>7053304</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6579,6 +6481,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6595,22 +6502,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6628,32 +6535,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123587645</v>
+        <v>123579421</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6661,19 +6563,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6687,13 +6580,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507096</v>
+        <v>507014</v>
       </c>
       <c r="R48" t="n">
-        <v>7053337</v>
+        <v>7053420</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6727,7 +6620,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6742,6 +6635,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6759,15 +6672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123580927</v>
+        <v>123580751</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6775,37 +6683,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507115</v>
+        <v>507106</v>
       </c>
       <c r="R49" t="n">
-        <v>7053483</v>
+        <v>7053481</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6837,6 +6755,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6786,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6886,15 +6809,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123585825</v>
+        <v>123582066</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6902,27 +6820,32 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6931,13 +6854,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507140</v>
+        <v>507073</v>
       </c>
       <c r="R50" t="n">
-        <v>7053422</v>
+        <v>7053530</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6969,6 +6892,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6995,12 +6923,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7018,15 +6946,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123582759</v>
+        <v>123588546</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7034,36 +6957,32 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7072,13 +6991,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507054</v>
+        <v>507024</v>
       </c>
       <c r="R51" t="n">
-        <v>7053507</v>
+        <v>7053316</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7108,6 +7027,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7159,15 +7083,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123583373</v>
+        <v>123590101</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7175,27 +7094,32 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7204,13 +7128,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>507030</v>
       </c>
       <c r="R52" t="n">
-        <v>7053507</v>
+        <v>7053146</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7242,6 +7166,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7268,12 +7197,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7291,15 +7220,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123586447</v>
+        <v>123590902</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7307,31 +7231,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7341,14 +7261,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
+          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507120</v>
+        <v>506945</v>
       </c>
       <c r="R53" t="n">
-        <v>7053421</v>
+        <v>7053117</v>
       </c>
       <c r="S53" t="n">
         <v>7</v>
@@ -7385,7 +7305,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7400,6 +7320,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7417,53 +7357,56 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123577656</v>
+        <v>122779296</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506944</v>
+        <v>507257</v>
       </c>
       <c r="R54" t="n">
-        <v>7053309</v>
+        <v>7053479</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7487,12 +7430,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7509,24 +7457,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad skog.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7544,53 +7477,67 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123582871</v>
+        <v>123587645</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507066</v>
+        <v>507096</v>
       </c>
       <c r="R55" t="n">
-        <v>7053479</v>
+        <v>7053337</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7622,6 +7569,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En sjungandes hane hördes i flerskiktad gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7634,26 +7586,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7671,15 +7603,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123588146</v>
+        <v>123586447</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7687,37 +7614,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Mårtengårdsbodarna, Brattmyrarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507059</v>
+        <v>507120</v>
       </c>
       <c r="R56" t="n">
-        <v>7053347</v>
+        <v>7053421</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7749,6 +7690,11 @@
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i flerskiktad gammal granskog med murkna björkhögtubbar för talltitan att bygga bo i.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7761,26 +7707,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7798,15 +7724,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123580202</v>
+        <v>91131050</v>
       </c>
       <c r="B57" t="n">
-        <v>79927</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7814,42 +7735,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>219847</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507014</v>
+        <v>507126</v>
       </c>
       <c r="R57" t="n">
-        <v>7053440</v>
+        <v>7053522</v>
       </c>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7873,12 +7789,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7890,55 +7806,39 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123576823</v>
+        <v>91131080</v>
       </c>
       <c r="B58" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7946,42 +7846,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>219847</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506940</v>
+        <v>506990</v>
       </c>
       <c r="R58" t="n">
-        <v>7053366</v>
+        <v>7053396</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8005,17 +7900,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På en grovbarkad sälglåga.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8027,98 +7917,77 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123585185</v>
+        <v>90798847</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Erik-Västlundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507197</v>
+        <v>506784</v>
       </c>
       <c r="R59" t="n">
-        <v>7053490</v>
+        <v>7053345</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8142,12 +8011,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8159,55 +8028,39 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123585014</v>
+        <v>91131054</v>
       </c>
       <c r="B60" t="n">
-        <v>91700</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8215,42 +8068,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>219880</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507278</v>
+        <v>507014</v>
       </c>
       <c r="R60" t="n">
-        <v>7053515</v>
+        <v>7053439</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8274,12 +8122,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8291,93 +8139,77 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123589076</v>
+        <v>91131069</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507050</v>
+        <v>507114</v>
       </c>
       <c r="R61" t="n">
-        <v>7053220</v>
+        <v>7053456</v>
       </c>
       <c r="S61" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8401,12 +8233,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8418,98 +8250,77 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123579984</v>
+        <v>91131075</v>
       </c>
       <c r="B62" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>219880</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507018</v>
+        <v>507047</v>
       </c>
       <c r="R62" t="n">
-        <v>7053429</v>
+        <v>7053171</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8533,12 +8344,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8550,83 +8361,67 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123583817</v>
+        <v>123579440</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8635,13 +8430,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507164</v>
+        <v>507010</v>
       </c>
       <c r="R63" t="n">
-        <v>7053542</v>
+        <v>7053401</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8681,31 +8476,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8722,53 +8492,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123584853</v>
+        <v>123589530</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>507238</v>
+        <v>507044</v>
       </c>
       <c r="R64" t="n">
-        <v>7053518</v>
+        <v>7053131</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8812,26 +8582,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8849,15 +8599,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123589530</v>
+        <v>91131044</v>
       </c>
       <c r="B65" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8865,42 +8610,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507044</v>
+        <v>507106</v>
       </c>
       <c r="R65" t="n">
-        <v>7053131</v>
+        <v>7053234</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8924,12 +8664,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8941,83 +8681,77 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123577590</v>
+        <v>91131051</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506932</v>
+        <v>507126</v>
       </c>
       <c r="R66" t="n">
-        <v>7053304</v>
+        <v>7053522</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9041,17 +8775,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack som bedöms vara 5-10 år gamla.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9063,96 +8792,77 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123772770</v>
+        <v>91131055</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507241</v>
+        <v>507014</v>
       </c>
       <c r="R67" t="n">
-        <v>7053498</v>
+        <v>7053439</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9176,17 +8886,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9195,107 +8900,80 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123579421</v>
+        <v>91131061</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507014</v>
+        <v>506900</v>
       </c>
       <c r="R68" t="n">
-        <v>7053420</v>
+        <v>7053298</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9319,17 +8997,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt med färska ringhack längs uppåt 10 meter på en något grövre gran. Kring fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9341,103 +9014,77 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123582066</v>
+        <v>91131071</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507073</v>
+        <v>507114</v>
       </c>
       <c r="R69" t="n">
-        <v>7053530</v>
+        <v>7053456</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9461,17 +9108,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en skadad gran. Här finns även äldre ringhack. Nära fyndplatsen finns avbarkade döda granar med färska potentiella födosökspår efter tretåig hackspett i minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9483,100 +9125,77 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123772501</v>
+        <v>91131081</v>
       </c>
       <c r="B70" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>507174</v>
+        <v>506990</v>
       </c>
       <c r="R70" t="n">
-        <v>7053322</v>
+        <v>7053396</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9600,12 +9219,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9614,107 +9233,80 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Gammal granskog med gott om stående död ved på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123581252</v>
+        <v>91131085</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>507113</v>
+        <v>506915</v>
       </c>
       <c r="R71" t="n">
-        <v>7053527</v>
+        <v>7053352</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9738,17 +9330,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav längs minst 4 meter på en hyfsat gammal sälg i gammal granskog.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9760,88 +9347,67 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123590902</v>
+        <v>123579557</v>
       </c>
       <c r="B72" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9850,13 +9416,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506945</v>
+        <v>507035</v>
       </c>
       <c r="R72" t="n">
-        <v>7053117</v>
+        <v>7053385</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9888,11 +9454,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack (skapade inom 5 år tillbaks) längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9901,31 +9462,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9942,48 +9478,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123580751</v>
+        <v>123591258</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9992,13 +9518,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507106</v>
+        <v>506882</v>
       </c>
       <c r="R73" t="n">
-        <v>7053481</v>
+        <v>7053247</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10030,11 +9556,6 @@
           <t>2025-03-29</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -10047,26 +9568,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10084,63 +9585,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123588546</v>
+        <v>91131070</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507024</v>
+        <v>507114</v>
       </c>
       <c r="R74" t="n">
-        <v>7053316</v>
+        <v>7053456</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10164,17 +9650,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med tydliga kådaflöden längs några meter på en gran.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10186,103 +9667,77 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123590101</v>
+        <v>91131079</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>222741</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mårtengårdsbodarna, Mårtengårdsbodarna, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507030</v>
+        <v>506910</v>
       </c>
       <c r="R75" t="n">
-        <v>7053146</v>
+        <v>7053170</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10306,17 +9761,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack längs flera meter på en gran. Kring fyndplatsen finns avbarkade döda granar med potentiella födosökspår efter tretåig hackspett i medelhöga till höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>2019-08-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10328,43 +9778,32 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2751-2025 artfynd.xlsx
+++ b/artfynd/A 2751-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779265</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123579984</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1056,6 +1071,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580416</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1188,6 +1208,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123588776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1320,6 +1345,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123584458</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1447,6 +1477,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585014</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1578,6 +1613,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779331</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1700,6 +1740,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123576556</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1822,6 +1867,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123577656</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1944,6 +1994,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580927</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2066,6 +2121,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123581420</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2198,6 +2258,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123582390</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2320,6 +2385,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123582871</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2442,6 +2512,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583184</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2569,6 +2644,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583373</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2691,6 +2771,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583498</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2818,6 +2903,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583817</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2940,6 +3030,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123584853</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3062,6 +3157,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585102</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3189,6 +3289,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585185</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3316,6 +3421,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585385</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3443,6 +3553,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585702</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3565,6 +3680,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123586717</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3687,6 +3807,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123587292</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3809,6 +3934,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123588146</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3931,6 +4061,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123589076</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4053,6 +4188,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123591099</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4184,6 +4324,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123772770</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4300,6 +4445,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90798960</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4416,6 +4566,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90798965</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4551,6 +4706,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779277</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4691,6 +4851,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779318</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4818,6 +4983,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123576777</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4945,6 +5115,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123577798</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5072,6 +5247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580175</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5204,6 +5384,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123581252</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5331,6 +5516,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583252</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5453,6 +5643,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123591471</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5585,6 +5780,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123576823</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5712,6 +5912,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580239</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5852,6 +6057,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779282</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5979,6 +6189,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580202</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6114,6 +6329,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779298</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6258,6 +6478,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779043</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6395,6 +6620,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123576291</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6532,6 +6762,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123577590</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6669,6 +6904,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123579421</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6806,6 +7046,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580751</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6943,6 +7188,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123582066</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7080,6 +7330,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123588546</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7217,6 +7472,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123590101</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7354,6 +7614,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123590902</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7474,6 +7739,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779296</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7600,6 +7870,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123587645</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7721,6 +7996,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123586447</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7832,6 +8112,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131050</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7943,6 +8228,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131080</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8054,6 +8344,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90798847</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8165,6 +8460,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131054</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8276,6 +8576,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131069</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8387,6 +8692,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131075</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8489,6 +8799,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123579440</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8596,6 +8911,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123589530</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8707,6 +9027,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131044</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8818,6 +9143,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131051</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8929,6 +9259,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131055</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9040,6 +9375,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131061</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9151,6 +9491,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131071</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9262,6 +9607,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131081</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9373,6 +9723,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131085</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9475,6 +9830,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123579557</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9582,6 +9942,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123591258</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9693,6 +10058,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131070</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9804,8 +10174,89 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131079</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>